--- a/5/search/FY2_Missile3_results/fine_tuned/all_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile3_results/fine_tuned/all_fine_tuned_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B2" t="n">
-        <v>134.7</v>
+        <v>132.2</v>
       </c>
       <c r="C2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>11922.95118449066</v>
+        <v>11852.81052842463</v>
       </c>
       <c r="F2" t="n">
-        <v>298.1506039260139</v>
+        <v>352.6924904989155</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>11874.09096002133</v>
+        <v>11751.61776671657</v>
       </c>
       <c r="I2" t="n">
-        <v>-400.5831594379772</v>
+        <v>-367.3314222830801</v>
       </c>
       <c r="J2" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6999999999999993</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B3" t="n">
-        <v>136.7</v>
+        <v>132.98</v>
       </c>
       <c r="C3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>11925.62146230559</v>
+        <v>11851.94208827464</v>
       </c>
       <c r="F3" t="n">
-        <v>336.3373557699599</v>
+        <v>346.5132177499679</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11876.03577050932</v>
+        <v>11750.15227396346</v>
       </c>
       <c r="I3" t="n">
-        <v>-372.7710737167334</v>
+        <v>-377.7589450469292</v>
       </c>
       <c r="J3" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K3" t="n">
-        <v>3.199999999999999</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -568,37 +568,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B4" t="n">
-        <v>137.7</v>
+        <v>133.76</v>
       </c>
       <c r="C4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E4" t="n">
-        <v>11925.07736181038</v>
+        <v>11851.07364812465</v>
       </c>
       <c r="F4" t="n">
-        <v>328.5563561779334</v>
+        <v>340.3339450010205</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>11875.12893635064</v>
+        <v>11748.68678121035</v>
       </c>
       <c r="I4" t="n">
-        <v>-385.7394063701112</v>
+        <v>-388.1864678107778</v>
       </c>
       <c r="J4" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K4" t="n">
-        <v>3.599999999999998</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -606,37 +606,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B5" t="n">
-        <v>138.7</v>
+        <v>137.66</v>
       </c>
       <c r="C5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E5" t="n">
-        <v>11924.53326131518</v>
+        <v>11858.2265888216</v>
       </c>
       <c r="F5" t="n">
-        <v>320.7753565859066</v>
+        <v>391.2297626620622</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>11874.22210219197</v>
+        <v>11752.8544588917</v>
       </c>
       <c r="I5" t="n">
-        <v>-398.707739023489</v>
+        <v>-358.5319002242429</v>
       </c>
       <c r="J5" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>267.6</v>
+        <v>262</v>
       </c>
       <c r="B6" t="n">
-        <v>134.7</v>
+        <v>138.44</v>
       </c>
       <c r="C6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>11951.49040520702</v>
+        <v>11857.42328168286</v>
       </c>
       <c r="F6" t="n">
-        <v>242.5961311568806</v>
+        <v>385.5139353692858</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>11924.41528253187</v>
+        <v>11751.45409914984</v>
       </c>
       <c r="I6" t="n">
-        <v>-403.3967258718371</v>
+        <v>-368.4959775319206</v>
       </c>
       <c r="J6" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1000000000000014</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>267.6</v>
+        <v>262</v>
       </c>
       <c r="B7" t="n">
-        <v>135.7</v>
+        <v>139.22</v>
       </c>
       <c r="C7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>11955.67629555379</v>
+        <v>11856.61997454411</v>
       </c>
       <c r="F7" t="n">
-        <v>342.4684492535625</v>
+        <v>379.7981080765095</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11926.12715925632</v>
+        <v>11750.05373940798</v>
       </c>
       <c r="I7" t="n">
-        <v>-362.5525845773959</v>
+        <v>-378.4600548395982</v>
       </c>
       <c r="J7" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K7" t="n">
-        <v>1.200000000000001</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
@@ -720,37 +720,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>267.6</v>
+        <v>262</v>
       </c>
       <c r="B8" t="n">
-        <v>136.7</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E8" t="n">
-        <v>11955.3496654547</v>
+        <v>11855.81666740537</v>
       </c>
       <c r="F8" t="n">
-        <v>334.6752911787914</v>
+        <v>374.0822807837333</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>11925.58277575784</v>
+        <v>11748.65337966612</v>
       </c>
       <c r="I8" t="n">
-        <v>-375.541181368681</v>
+        <v>-388.4241321472758</v>
       </c>
       <c r="J8" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K8" t="n">
-        <v>3.700000000000001</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>267.6</v>
+        <v>263.6</v>
       </c>
       <c r="B9" t="n">
-        <v>137.7</v>
+        <v>132.2</v>
       </c>
       <c r="C9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E9" t="n">
-        <v>11955.02303535562</v>
+        <v>11882.11045729859</v>
       </c>
       <c r="F9" t="n">
-        <v>326.8821331040203</v>
+        <v>348.9910486957533</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11925.03839225936</v>
+        <v>11801.06139669137</v>
       </c>
       <c r="I9" t="n">
-        <v>-388.5297781599662</v>
+        <v>-373.5776053259162</v>
       </c>
       <c r="J9" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>267.6</v>
+        <v>263.6</v>
       </c>
       <c r="B10" t="n">
-        <v>137.7</v>
+        <v>132.98</v>
       </c>
       <c r="C10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E10" t="n">
-        <v>11952.71652434821</v>
+        <v>11881.41489116162</v>
       </c>
       <c r="F10" t="n">
-        <v>271.8504476221754</v>
+        <v>342.7899368801911</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11925.03839225936</v>
+        <v>11799.88762883524</v>
       </c>
       <c r="I10" t="n">
-        <v>-388.5297781599661</v>
+        <v>-384.0419815146774</v>
       </c>
       <c r="J10" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3000000000000007</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>267.6</v>
+        <v>263.6</v>
       </c>
       <c r="B11" t="n">
-        <v>138.7</v>
+        <v>136.88</v>
       </c>
       <c r="C11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="n">
-        <v>11952.37314398763</v>
+        <v>11887.09178094103</v>
       </c>
       <c r="F11" t="n">
-        <v>263.6576404153648</v>
+        <v>393.4005494672019</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>11924.49400876088</v>
+        <v>11803.17351001882</v>
       </c>
       <c r="I11" t="n">
-        <v>-401.5183749512512</v>
+        <v>-354.7476907936615</v>
       </c>
       <c r="J11" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
@@ -872,37 +872,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>269.2</v>
+        <v>263.6</v>
       </c>
       <c r="B12" t="n">
-        <v>134.7</v>
+        <v>137.66</v>
       </c>
       <c r="C12" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E12" t="n">
-        <v>11983.82593105153</v>
+        <v>11886.44838226433</v>
       </c>
       <c r="F12" t="n">
-        <v>241.692918137142</v>
+        <v>387.6645210378069</v>
       </c>
       <c r="G12" t="n">
         <v>1400</v>
       </c>
       <c r="H12" t="n">
-        <v>11974.79854373145</v>
+        <v>11802.05190962296</v>
       </c>
       <c r="I12" t="n">
-        <v>-404.8040577863135</v>
+        <v>-364.7469835962554</v>
       </c>
       <c r="J12" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6999999999999993</v>
+        <v>3.299999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -910,37 +910,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>269.2</v>
+        <v>263.6</v>
       </c>
       <c r="B13" t="n">
-        <v>135.7</v>
+        <v>138.44</v>
       </c>
       <c r="C13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E13" t="n">
-        <v>11985.22159059823</v>
+        <v>11885.80498358764</v>
       </c>
       <c r="F13" t="n">
-        <v>341.6431744371118</v>
+        <v>381.9284926084119</v>
       </c>
       <c r="G13" t="n">
         <v>1400</v>
       </c>
       <c r="H13" t="n">
-        <v>11975.36931766371</v>
+        <v>11800.9303092271</v>
       </c>
       <c r="I13" t="n">
-        <v>-363.9280426048135</v>
+        <v>-374.7462763988494</v>
       </c>
       <c r="J13" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K13" t="n">
-        <v>1.200000000000001</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -948,37 +948,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>269.2</v>
+        <v>263.6</v>
       </c>
       <c r="B14" t="n">
-        <v>136.7</v>
+        <v>138.44</v>
       </c>
       <c r="C14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>11985.11268559158</v>
+        <v>11876.54592820285</v>
       </c>
       <c r="F14" t="n">
-        <v>333.8439347498393</v>
+        <v>299.3821541712562</v>
       </c>
       <c r="G14" t="n">
         <v>1400</v>
       </c>
       <c r="H14" t="n">
-        <v>11975.1878093193</v>
+        <v>11799.38713332963</v>
       </c>
       <c r="I14" t="n">
-        <v>-376.9267754169346</v>
+        <v>-388.5039994717088</v>
       </c>
       <c r="J14" t="n">
-        <v>1267.504</v>
+        <v>1277.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -986,37 +986,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>269.2</v>
+        <v>265.2</v>
       </c>
       <c r="B15" t="n">
-        <v>137.7</v>
+        <v>132.2</v>
       </c>
       <c r="C15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E15" t="n">
-        <v>11984.23474369186</v>
+        <v>11911.50231289174</v>
       </c>
       <c r="F15" t="n">
-        <v>270.9700640401345</v>
+        <v>346.1091520577245</v>
       </c>
       <c r="G15" t="n">
         <v>1400</v>
       </c>
       <c r="H15" t="n">
-        <v>11975.0063009749</v>
+        <v>11850.66015300482</v>
       </c>
       <c r="I15" t="n">
-        <v>-389.9255082290553</v>
+        <v>-378.4408059025899</v>
       </c>
       <c r="J15" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K15" t="n">
-        <v>2.800000000000001</v>
+        <v>1.200000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
@@ -1024,37 +1024,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>269.2</v>
+        <v>265.2</v>
       </c>
       <c r="B16" t="n">
-        <v>138.7</v>
+        <v>132.2</v>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>11984.12025381308</v>
+        <v>11904.86498635862</v>
       </c>
       <c r="F16" t="n">
-        <v>262.770863343258</v>
+        <v>267.0673384620538</v>
       </c>
       <c r="G16" t="n">
         <v>1400</v>
       </c>
       <c r="H16" t="n">
-        <v>11974.82479263049</v>
+        <v>11849.55393191596</v>
       </c>
       <c r="I16" t="n">
-        <v>-402.9242410411764</v>
+        <v>-391.6144415018683</v>
       </c>
       <c r="J16" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.099999999999998</v>
+        <v>1.400000000000002</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1062,37 +1062,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>269.2</v>
+        <v>265.2</v>
       </c>
       <c r="B17" t="n">
-        <v>139.7</v>
+        <v>132.98</v>
       </c>
       <c r="C17" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>11985.566177209</v>
+        <v>11904.30367538555</v>
       </c>
       <c r="F17" t="n">
-        <v>366.3207687296615</v>
+        <v>260.3828643622082</v>
       </c>
       <c r="G17" t="n">
         <v>1400</v>
       </c>
       <c r="H17" t="n">
-        <v>11975.42349092343</v>
+        <v>11848.66627735389</v>
       </c>
       <c r="I17" t="n">
-        <v>-360.0484208116576</v>
+        <v>-402.1852377527871</v>
       </c>
       <c r="J17" t="n">
-        <v>1267.504</v>
+        <v>1277.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0.2000000000000028</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
@@ -1100,37 +1100,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>270.8</v>
+        <v>265.2</v>
       </c>
       <c r="B18" t="n">
-        <v>134.7</v>
+        <v>136.88</v>
       </c>
       <c r="C18" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="D18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E18" t="n">
-        <v>12016.17406894847</v>
+        <v>11915.24170835458</v>
       </c>
       <c r="F18" t="n">
-        <v>241.692918137142</v>
+        <v>390.6404249518662</v>
       </c>
       <c r="G18" t="n">
         <v>1400</v>
       </c>
       <c r="H18" t="n">
-        <v>12025.20145626855</v>
+        <v>11852.24568078028</v>
       </c>
       <c r="I18" t="n">
-        <v>-404.8040577863135</v>
+        <v>-359.5592592055306</v>
       </c>
       <c r="J18" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K18" t="n">
-        <v>1.199999999999999</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1138,37 +1138,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>270.8</v>
+        <v>265.2</v>
       </c>
       <c r="B19" t="n">
-        <v>135.7</v>
+        <v>137.66</v>
       </c>
       <c r="C19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E19" t="n">
-        <v>12014.77840940177</v>
+        <v>11914.75871984286</v>
       </c>
       <c r="F19" t="n">
-        <v>341.6431744371118</v>
+        <v>384.8886681682781</v>
       </c>
       <c r="G19" t="n">
         <v>1400</v>
       </c>
       <c r="H19" t="n">
-        <v>12024.63068233629</v>
+        <v>11851.40371432067</v>
       </c>
       <c r="I19" t="n">
-        <v>-363.9280426048135</v>
+        <v>-369.5859703552991</v>
       </c>
       <c r="J19" t="n">
-        <v>1267.504</v>
+        <v>1251.775</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3000000000000007</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1176,37 +1176,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>270.8</v>
+        <v>265.2</v>
       </c>
       <c r="B20" t="n">
-        <v>136.7</v>
+        <v>137.66</v>
       </c>
       <c r="C20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>12014.88731440842</v>
+        <v>11907.84726469499</v>
       </c>
       <c r="F20" t="n">
-        <v>333.8439347498393</v>
+        <v>302.5823439657061</v>
       </c>
       <c r="G20" t="n">
         <v>1400</v>
       </c>
       <c r="H20" t="n">
-        <v>12024.8121906807</v>
+        <v>11850.25180512935</v>
       </c>
       <c r="I20" t="n">
-        <v>-376.9267754169346</v>
+        <v>-383.3036910557277</v>
       </c>
       <c r="J20" t="n">
-        <v>1267.504</v>
+        <v>1277.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.100000000000001</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1214,37 +1214,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>270.8</v>
+        <v>265.2</v>
       </c>
       <c r="B21" t="n">
-        <v>137.7</v>
+        <v>138.44</v>
       </c>
       <c r="C21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>12015.76525630814</v>
+        <v>11907.32511495259</v>
       </c>
       <c r="F21" t="n">
-        <v>270.9700640401345</v>
+        <v>296.3642285239891</v>
       </c>
       <c r="G21" t="n">
         <v>1400</v>
       </c>
       <c r="H21" t="n">
-        <v>12024.9936990251</v>
+        <v>11849.40331179796</v>
       </c>
       <c r="I21" t="n">
-        <v>-389.9255082290553</v>
+        <v>-393.4081286485176</v>
       </c>
       <c r="J21" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -1252,37 +1252,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>270.8</v>
+        <v>265.2</v>
       </c>
       <c r="B22" t="n">
-        <v>138.7</v>
+        <v>139.22</v>
       </c>
       <c r="C22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>12015.87974618692</v>
+        <v>11906.8029652102</v>
       </c>
       <c r="F22" t="n">
-        <v>262.770863343258</v>
+        <v>290.1461130822722</v>
       </c>
       <c r="G22" t="n">
         <v>1400</v>
       </c>
       <c r="H22" t="n">
-        <v>12025.17520736951</v>
+        <v>11848.55481846657</v>
       </c>
       <c r="I22" t="n">
-        <v>-402.9242410411764</v>
+        <v>-403.5125662413077</v>
       </c>
       <c r="J22" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K22" t="n">
-        <v>1.600000000000001</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -1290,37 +1290,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>272.4</v>
+        <v>266.8</v>
       </c>
       <c r="B23" t="n">
-        <v>134.7</v>
+        <v>132.2</v>
       </c>
       <c r="C23" t="n">
         <v>8.6</v>
       </c>
       <c r="D23" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>12048.50959479298</v>
+        <v>11936.53541454317</v>
       </c>
       <c r="F23" t="n">
-        <v>242.5961311568806</v>
+        <v>264.8527263862225</v>
       </c>
       <c r="G23" t="n">
         <v>1400</v>
       </c>
       <c r="H23" t="n">
-        <v>12075.58471746813</v>
+        <v>11899.63739974269</v>
       </c>
       <c r="I23" t="n">
-        <v>-403.3967258718371</v>
+        <v>-395.1166187380669</v>
       </c>
       <c r="J23" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K23" t="n">
-        <v>1.800000000000001</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -1328,37 +1328,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>272.4</v>
+        <v>266.8</v>
       </c>
       <c r="B24" t="n">
-        <v>136.7</v>
+        <v>132.98</v>
       </c>
       <c r="C24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>12044.6503345453</v>
+        <v>11936.16096388768</v>
       </c>
       <c r="F24" t="n">
-        <v>334.6752911787914</v>
+        <v>258.1551857400896</v>
       </c>
       <c r="G24" t="n">
         <v>1400</v>
       </c>
       <c r="H24" t="n">
-        <v>12074.41722424216</v>
+        <v>11899.04524521772</v>
       </c>
       <c r="I24" t="n">
-        <v>-375.541181368681</v>
+        <v>-405.7080783645096</v>
       </c>
       <c r="J24" t="n">
-        <v>1267.504</v>
+        <v>1277.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3000000000000007</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1366,37 +1366,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>272.4</v>
+        <v>266.8</v>
       </c>
       <c r="B25" t="n">
-        <v>136.7</v>
+        <v>136.88</v>
       </c>
       <c r="C25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D25" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E25" t="n">
-        <v>12046.94009529121</v>
+        <v>11943.45772773436</v>
       </c>
       <c r="F25" t="n">
-        <v>280.0432548289859</v>
+        <v>388.6673686709012</v>
       </c>
       <c r="G25" t="n">
         <v>1400</v>
       </c>
       <c r="H25" t="n">
-        <v>12074.41722424216</v>
+        <v>11901.43306591531</v>
       </c>
       <c r="I25" t="n">
-        <v>-375.541181368681</v>
+        <v>-362.9987762358614</v>
       </c>
       <c r="J25" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>0.7000000000000011</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1404,37 +1404,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>272.4</v>
+        <v>266.8</v>
       </c>
       <c r="B26" t="n">
-        <v>137.7</v>
+        <v>136.88</v>
       </c>
       <c r="C26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>12047.28347565179</v>
+        <v>11938.87321917228</v>
       </c>
       <c r="F26" t="n">
-        <v>271.8504476221754</v>
+        <v>306.6674255901635</v>
       </c>
       <c r="G26" t="n">
         <v>1400</v>
       </c>
       <c r="H26" t="n">
-        <v>12074.96160774064</v>
+        <v>11900.66898115496</v>
       </c>
       <c r="I26" t="n">
-        <v>-388.5297781599661</v>
+        <v>-376.6654334159844</v>
       </c>
       <c r="J26" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.699999999999999</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1442,37 +1442,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>272.4</v>
+        <v>266.8</v>
       </c>
       <c r="B27" t="n">
-        <v>138.7</v>
+        <v>137.66</v>
       </c>
       <c r="C27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>12047.62685601237</v>
+        <v>11938.52489298113</v>
       </c>
       <c r="F27" t="n">
-        <v>263.6576404153648</v>
+        <v>300.437155221668</v>
       </c>
       <c r="G27" t="n">
         <v>1400</v>
       </c>
       <c r="H27" t="n">
-        <v>12075.50599123912</v>
+        <v>11900.10295109433</v>
       </c>
       <c r="I27" t="n">
-        <v>-401.5183749512512</v>
+        <v>-386.7896227647894</v>
       </c>
       <c r="J27" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2.200000000000003</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>3</v>
@@ -1480,37 +1480,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>274</v>
+        <v>266.8</v>
       </c>
       <c r="B28" t="n">
-        <v>134.7</v>
+        <v>138.44</v>
       </c>
       <c r="C28" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>12080.80729431467</v>
+        <v>11938.17656678997</v>
       </c>
       <c r="F28" t="n">
-        <v>244.4018528980143</v>
+        <v>294.2068848531724</v>
       </c>
       <c r="G28" t="n">
         <v>1400</v>
       </c>
       <c r="H28" t="n">
-        <v>12125.90903997867</v>
+        <v>11899.5369210337</v>
       </c>
       <c r="I28" t="n">
-        <v>-400.5831594379775</v>
+        <v>-396.9138121135949</v>
       </c>
       <c r="J28" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1.900000000000002</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1518,37 +1518,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="B29" t="n">
-        <v>134.7</v>
+        <v>132.2</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="D29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>12084.56577312</v>
+        <v>11968.2553305024</v>
       </c>
       <c r="F29" t="n">
-        <v>190.653101870015</v>
+        <v>263.5232680083204</v>
       </c>
       <c r="G29" t="n">
         <v>1400</v>
       </c>
       <c r="H29" t="n">
-        <v>12125.90903997867</v>
+        <v>11949.79912730612</v>
       </c>
       <c r="I29" t="n">
-        <v>-400.5831594379777</v>
+        <v>-397.2190180333537</v>
       </c>
       <c r="J29" t="n">
-        <v>1305.136</v>
+        <v>1277.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.300000000000001</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>3</v>
@@ -1556,37 +1556,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="B30" t="n">
-        <v>136.7</v>
+        <v>136.88</v>
       </c>
       <c r="C30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>12078.19282167874</v>
+        <v>11969.42468873214</v>
       </c>
       <c r="F30" t="n">
-        <v>281.7905535017526</v>
+        <v>305.3869396262105</v>
       </c>
       <c r="G30" t="n">
         <v>1400</v>
       </c>
       <c r="H30" t="n">
-        <v>12123.96422949068</v>
+        <v>11950.31511918973</v>
       </c>
       <c r="I30" t="n">
-        <v>-372.7710737167338</v>
+        <v>-378.7462231074079</v>
       </c>
       <c r="J30" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1.600000000000001</v>
+        <v>2.999999999999998</v>
       </c>
       <c r="L30" t="n">
         <v>3</v>
@@ -1594,37 +1594,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="B31" t="n">
-        <v>137.7</v>
+        <v>137.66</v>
       </c>
       <c r="C31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>12078.76482476344</v>
+        <v>11969.25045770651</v>
       </c>
       <c r="F31" t="n">
-        <v>273.6105282896222</v>
+        <v>299.1493725083585</v>
       </c>
       <c r="G31" t="n">
         <v>1400</v>
       </c>
       <c r="H31" t="n">
-        <v>12124.87106364936</v>
+        <v>11950.03199377308</v>
       </c>
       <c r="I31" t="n">
-        <v>-385.7394063701114</v>
+        <v>-388.8822696739174</v>
       </c>
       <c r="J31" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.800000000000001</v>
+        <v>3.700000000000003</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -1632,37 +1632,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="B32" t="n">
-        <v>138.7</v>
+        <v>138.44</v>
       </c>
       <c r="C32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>12079.33682784814</v>
+        <v>11969.07622668087</v>
       </c>
       <c r="F32" t="n">
-        <v>265.4305030774915</v>
+        <v>292.9118053905067</v>
       </c>
       <c r="G32" t="n">
         <v>1400</v>
       </c>
       <c r="H32" t="n">
-        <v>12125.77789780803</v>
+        <v>11949.74886835642</v>
       </c>
       <c r="I32" t="n">
-        <v>-398.7077390234892</v>
+        <v>-399.0183162404265</v>
       </c>
       <c r="J32" t="n">
-        <v>1287.104</v>
+        <v>1277.5</v>
       </c>
       <c r="K32" t="n">
-        <v>1.800000000000001</v>
+        <v>1.900000000000002</v>
       </c>
       <c r="L32" t="n">
         <v>3</v>
@@ -1670,37 +1670,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B33" t="n">
-        <v>138.7</v>
+        <v>132.2</v>
       </c>
       <c r="C33" t="n">
         <v>8.6</v>
       </c>
       <c r="D33" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>12083.20691701147</v>
+        <v>12000</v>
       </c>
       <c r="F33" t="n">
-        <v>210.0856495690764</v>
+        <v>263.0800000000002</v>
       </c>
       <c r="G33" t="n">
         <v>1400</v>
       </c>
       <c r="H33" t="n">
-        <v>12125.77789780803</v>
+        <v>12000</v>
       </c>
       <c r="I33" t="n">
-        <v>-398.7077390234892</v>
+        <v>-397.9199999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>1305.136</v>
+        <v>1277.5</v>
       </c>
       <c r="K33" t="n">
-        <v>1.699999999999999</v>
+        <v>2.500000000000004</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -1708,37 +1708,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B34" t="n">
-        <v>139.7</v>
+        <v>136.1</v>
       </c>
       <c r="C34" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>12083.80682268567</v>
+        <v>12000</v>
       </c>
       <c r="F34" t="n">
-        <v>201.5065987368421</v>
+        <v>311.2</v>
       </c>
       <c r="G34" t="n">
         <v>1400</v>
       </c>
       <c r="H34" t="n">
-        <v>12126.6847319667</v>
+        <v>12000</v>
       </c>
       <c r="I34" t="n">
-        <v>-411.6760716768666</v>
+        <v>-369.3</v>
       </c>
       <c r="J34" t="n">
-        <v>1305.136</v>
+        <v>1277.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1999999999999993</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -1746,3231 +1746,7069 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B35" t="n">
-        <v>101.1</v>
+        <v>136.88</v>
       </c>
       <c r="C35" t="n">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>11537.95273554895</v>
+        <v>12000</v>
       </c>
       <c r="F35" t="n">
-        <v>256.3928901002334</v>
+        <v>304.96</v>
       </c>
       <c r="G35" t="n">
         <v>1400</v>
       </c>
       <c r="H35" t="n">
-        <v>11287.99274002624</v>
+        <v>12000</v>
       </c>
       <c r="I35" t="n">
-        <v>-362.2798086980008</v>
+        <v>-379.4399999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>1186.556</v>
+        <v>1277.5</v>
       </c>
       <c r="K35" t="n">
-        <v>1.400000000000002</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B36" t="n">
-        <v>103.1</v>
+        <v>137.66</v>
       </c>
       <c r="C36" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>11544.26111058207</v>
+        <v>12000</v>
       </c>
       <c r="F36" t="n">
-        <v>272.0066662111378</v>
+        <v>298.72</v>
       </c>
       <c r="G36" t="n">
         <v>1400</v>
       </c>
       <c r="H36" t="n">
-        <v>11289.35630802628</v>
+        <v>12000</v>
       </c>
       <c r="I36" t="n">
-        <v>-358.9048594673781</v>
+        <v>-389.5799999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>1186.556</v>
+        <v>1277.5</v>
       </c>
       <c r="K36" t="n">
-        <v>1.199999999999999</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B37" t="n">
-        <v>104.1</v>
+        <v>138.44</v>
       </c>
       <c r="C37" t="n">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>11524.24213422992</v>
+        <v>12000</v>
       </c>
       <c r="F37" t="n">
-        <v>222.457961023089</v>
+        <v>292.48</v>
       </c>
       <c r="G37" t="n">
         <v>1400</v>
       </c>
       <c r="H37" t="n">
-        <v>11282.46354670743</v>
+        <v>12000</v>
       </c>
       <c r="I37" t="n">
-        <v>-375.9650423914068</v>
+        <v>-399.72</v>
       </c>
       <c r="J37" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>248</v>
+        <v>271.6</v>
       </c>
       <c r="B38" t="n">
-        <v>105.1</v>
+        <v>132.2</v>
       </c>
       <c r="C38" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="D38" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>11551.16885616466</v>
+        <v>12031.7446694976</v>
       </c>
       <c r="F38" t="n">
-        <v>289.1039364893495</v>
+        <v>263.5232680083204</v>
       </c>
       <c r="G38" t="n">
         <v>1400</v>
       </c>
       <c r="H38" t="n">
-        <v>11291.31924657578</v>
+        <v>12050.20087269388</v>
       </c>
       <c r="I38" t="n">
-        <v>-354.0464160694481</v>
+        <v>-397.2190180333537</v>
       </c>
       <c r="J38" t="n">
-        <v>1186.556</v>
+        <v>1277.5</v>
       </c>
       <c r="K38" t="n">
         <v>0.8000000000000007</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>248</v>
+        <v>271.6</v>
       </c>
       <c r="B39" t="n">
-        <v>106.1</v>
+        <v>136.1</v>
       </c>
       <c r="C39" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>11531.00003717515</v>
+        <v>12030.40108024222</v>
       </c>
       <c r="F39" t="n">
-        <v>239.1843577594736</v>
+        <v>311.6245067440623</v>
       </c>
       <c r="G39" t="n">
         <v>1400</v>
       </c>
       <c r="H39" t="n">
-        <v>11284.57632789429</v>
+        <v>12049.40175539361</v>
       </c>
       <c r="I39" t="n">
-        <v>-370.7357254516503</v>
+        <v>-368.6101765408988</v>
       </c>
       <c r="J39" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K39" t="n">
-        <v>1.100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>249.6</v>
+        <v>271.6</v>
       </c>
       <c r="B40" t="n">
-        <v>101.1</v>
+        <v>136.88</v>
       </c>
       <c r="C40" t="n">
-        <v>12.6</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>11555.96801179863</v>
+        <v>12030.57531126786</v>
       </c>
       <c r="F40" t="n">
-        <v>206.0339648658592</v>
+        <v>305.3869396262105</v>
       </c>
       <c r="G40" t="n">
         <v>1400</v>
       </c>
       <c r="H40" t="n">
-        <v>11337.47608109637</v>
+        <v>12049.68488081027</v>
       </c>
       <c r="I40" t="n">
-        <v>-381.4731317874483</v>
+        <v>-378.7462231074079</v>
       </c>
       <c r="J40" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8000000000000007</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>249.6</v>
+        <v>271.6</v>
       </c>
       <c r="B41" t="n">
-        <v>103.1</v>
+        <v>137.66</v>
       </c>
       <c r="C41" t="n">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>11561.55910743767</v>
+        <v>12030.74954229349</v>
       </c>
       <c r="F41" t="n">
-        <v>221.0679679773091</v>
+        <v>299.1493725083585</v>
       </c>
       <c r="G41" t="n">
         <v>1400</v>
       </c>
       <c r="H41" t="n">
-        <v>11338.74488334862</v>
+        <v>12049.96800622693</v>
       </c>
       <c r="I41" t="n">
-        <v>-378.0614253456977</v>
+        <v>-388.8822696739174</v>
       </c>
       <c r="J41" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K41" t="n">
-        <v>1.400000000000002</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>249.6</v>
+        <v>271.6</v>
       </c>
       <c r="B42" t="n">
-        <v>105.1</v>
+        <v>137.66</v>
       </c>
       <c r="C42" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="D42" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E42" t="n">
-        <v>11567.70791835243</v>
+        <v>12033.05575796551</v>
       </c>
       <c r="F42" t="n">
-        <v>237.6016222719461</v>
+        <v>216.5855754464853</v>
       </c>
       <c r="G42" t="n">
         <v>1400</v>
       </c>
       <c r="H42" t="n">
-        <v>11340.57140087659</v>
+        <v>12050.35237550559</v>
       </c>
       <c r="I42" t="n">
-        <v>-373.15006772076</v>
+        <v>-402.642902517563</v>
       </c>
       <c r="J42" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K42" t="n">
-        <v>2.199999999999999</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>251.2</v>
+        <v>273.2</v>
       </c>
       <c r="B43" t="n">
-        <v>101.1</v>
+        <v>132.2</v>
       </c>
       <c r="C43" t="n">
-        <v>12.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E43" t="n">
-        <v>11602.51104618878</v>
+        <v>12067.89234723289</v>
       </c>
       <c r="F43" t="n">
-        <v>232.3838695880982</v>
+        <v>185.6564049713077</v>
       </c>
       <c r="G43" t="n">
         <v>1400</v>
       </c>
       <c r="H43" t="n">
-        <v>11400.50846310439</v>
+        <v>12101.10056055332</v>
       </c>
       <c r="I43" t="n">
-        <v>-360.9948196376225</v>
+        <v>-408.3160056405527</v>
       </c>
       <c r="J43" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K43" t="n">
-        <v>1.800000000000001</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>251.2</v>
+        <v>273.2</v>
       </c>
       <c r="B44" t="n">
-        <v>102.1</v>
+        <v>136.1</v>
       </c>
       <c r="C44" t="n">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>11598.57940470697</v>
+        <v>12060.77845463656</v>
       </c>
       <c r="F44" t="n">
-        <v>220.8347486146865</v>
+        <v>312.8976959586591</v>
       </c>
       <c r="G44" t="n">
         <v>1400</v>
       </c>
       <c r="H44" t="n">
-        <v>11394.57877431215</v>
+        <v>12098.7649887844</v>
       </c>
       <c r="I44" t="n">
-        <v>-378.4131660237515</v>
+        <v>-366.5412440671789</v>
       </c>
       <c r="J44" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K44" t="n">
-        <v>2.100000000000001</v>
+        <v>0.2000000000000011</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>251.2</v>
+        <v>273.2</v>
       </c>
       <c r="B45" t="n">
-        <v>103.1</v>
+        <v>136.88</v>
       </c>
       <c r="C45" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>11607.93800049646</v>
+        <v>12061.12678082771</v>
       </c>
       <c r="F45" t="n">
-        <v>248.3254431284463</v>
+        <v>306.6674255901635</v>
       </c>
       <c r="G45" t="n">
         <v>1400</v>
       </c>
       <c r="H45" t="n">
-        <v>11401.93932279122</v>
+        <v>12099.33101884503</v>
       </c>
       <c r="I45" t="n">
-        <v>-356.791696922709</v>
+        <v>-376.6654334159844</v>
       </c>
       <c r="J45" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K45" t="n">
-        <v>1.100000000000001</v>
+        <v>2.200000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>251.2</v>
+        <v>273.2</v>
       </c>
       <c r="B46" t="n">
-        <v>104.1</v>
+        <v>136.88</v>
       </c>
       <c r="C46" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="D46" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E46" t="n">
-        <v>11604.13526529275</v>
+        <v>12065.71128938979</v>
       </c>
       <c r="F46" t="n">
-        <v>237.1549818590811</v>
+        <v>224.6674825094258</v>
       </c>
       <c r="G46" t="n">
         <v>1400</v>
       </c>
       <c r="H46" t="n">
-        <v>11396.13854027707</v>
+        <v>12100.09510360538</v>
       </c>
       <c r="I46" t="n">
-        <v>-373.8313836047914</v>
+        <v>-390.3320905961073</v>
       </c>
       <c r="J46" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K46" t="n">
+        <v>0.5999999999999979</v>
+      </c>
+      <c r="L46" t="n">
         <v>3</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>251.2</v>
+        <v>273.2</v>
       </c>
       <c r="B47" t="n">
-        <v>106.1</v>
+        <v>137.66</v>
       </c>
       <c r="C47" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>11610.20675099089</v>
+        <v>12061.47510701887</v>
       </c>
       <c r="F47" t="n">
-        <v>254.9898539196606</v>
+        <v>300.437155221668</v>
       </c>
       <c r="G47" t="n">
         <v>1400</v>
       </c>
       <c r="H47" t="n">
-        <v>11398.21393135435</v>
+        <v>12099.89704890567</v>
       </c>
       <c r="I47" t="n">
-        <v>-367.7349623696468</v>
+        <v>-386.7896227647894</v>
       </c>
       <c r="J47" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K47" t="n">
-        <v>3.5</v>
+        <v>1.799999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>252.8</v>
+        <v>273.2</v>
       </c>
       <c r="B48" t="n">
-        <v>101.1</v>
+        <v>137.66</v>
       </c>
       <c r="C48" t="n">
-        <v>12.2</v>
+        <v>8.6</v>
       </c>
       <c r="D48" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E48" t="n">
-        <v>11635.26777691467</v>
+        <v>12066.08574004529</v>
       </c>
       <c r="F48" t="n">
-        <v>221.7405625910592</v>
+        <v>217.9699418632931</v>
       </c>
       <c r="G48" t="n">
         <v>1400</v>
       </c>
       <c r="H48" t="n">
-        <v>11449.91205698606</v>
+        <v>12100.6654877434</v>
       </c>
       <c r="I48" t="n">
-        <v>-377.0470203544681</v>
+        <v>-400.5341583245186</v>
       </c>
       <c r="J48" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K48" t="n">
-        <v>2.899999999999999</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>252.8</v>
+        <v>273.2</v>
       </c>
       <c r="B49" t="n">
-        <v>102.1</v>
+        <v>138.44</v>
       </c>
       <c r="C49" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="D49" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E49" t="n">
-        <v>11643.73685546793</v>
+        <v>12066.46019070078</v>
       </c>
       <c r="F49" t="n">
-        <v>249.099734882243</v>
+        <v>211.2724012171604</v>
       </c>
       <c r="G49" t="n">
         <v>1400</v>
       </c>
       <c r="H49" t="n">
-        <v>11456.54774562905</v>
+        <v>12101.23587188142</v>
       </c>
       <c r="I49" t="n">
-        <v>-355.6105739084429</v>
+        <v>-410.7362260529301</v>
       </c>
       <c r="J49" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>0.4000000000000021</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>252.8</v>
+        <v>274.8</v>
       </c>
       <c r="B50" t="n">
-        <v>103.1</v>
+        <v>132.2</v>
       </c>
       <c r="C50" t="n">
-        <v>11.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E50" t="n">
-        <v>11640.24750047741</v>
+        <v>12101.7723401745</v>
       </c>
       <c r="F50" t="n">
-        <v>237.8274502091992</v>
+        <v>188.025524866383</v>
       </c>
       <c r="G50" t="n">
         <v>1400</v>
       </c>
       <c r="H50" t="n">
-        <v>11451.22500072826</v>
+        <v>12151.55228917289</v>
       </c>
       <c r="I50" t="n">
-        <v>-372.8055844266452</v>
+        <v>-404.7880771011471</v>
       </c>
       <c r="J50" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K50" t="n">
-        <v>3.300000000000001</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>252.8</v>
+        <v>274.8</v>
       </c>
       <c r="B51" t="n">
-        <v>105.1</v>
+        <v>136.88</v>
       </c>
       <c r="C51" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>11645.70035692023</v>
+        <v>12091.63058556262</v>
       </c>
       <c r="F51" t="n">
-        <v>255.4427832067352</v>
+        <v>308.8004594074227</v>
       </c>
       <c r="G51" t="n">
         <v>1400</v>
       </c>
       <c r="H51" t="n">
-        <v>11453.01107735052</v>
+        <v>12148.89970153925</v>
       </c>
       <c r="I51" t="n">
-        <v>-367.0357031194266</v>
+        <v>-373.199253462938</v>
       </c>
       <c r="J51" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2.899999999999999</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>252.8</v>
+        <v>274.8</v>
       </c>
       <c r="B52" t="n">
-        <v>106.1</v>
+        <v>136.88</v>
       </c>
       <c r="C52" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="D52" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E52" t="n">
-        <v>11642.32928514972</v>
+        <v>12098.50287947981</v>
       </c>
       <c r="F52" t="n">
-        <v>244.5526098785404</v>
+        <v>226.9604938629795</v>
       </c>
       <c r="G52" t="n">
         <v>1400</v>
       </c>
       <c r="H52" t="n">
-        <v>11447.80661566975</v>
+        <v>12150.04508385879</v>
       </c>
       <c r="I52" t="n">
-        <v>-383.8486022927799</v>
+        <v>-386.8392477203452</v>
       </c>
       <c r="J52" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K52" t="n">
-        <v>0.6999999999999993</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254.4</v>
+        <v>274.8</v>
       </c>
       <c r="B53" t="n">
-        <v>102.1</v>
+        <v>137.66</v>
       </c>
       <c r="C53" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>11676.01077851914</v>
+        <v>12092.15273530501</v>
       </c>
       <c r="F53" t="n">
-        <v>239.6010027735174</v>
+        <v>302.5823439657058</v>
       </c>
       <c r="G53" t="n">
         <v>1400</v>
       </c>
       <c r="H53" t="n">
-        <v>11505.77915367326</v>
+        <v>12149.74819487064</v>
       </c>
       <c r="I53" t="n">
-        <v>-370.100165260736</v>
+        <v>-383.303691055728</v>
       </c>
       <c r="J53" t="n">
-        <v>1211.644</v>
+        <v>1277.5</v>
       </c>
       <c r="K53" t="n">
-        <v>1.900000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254.4</v>
+        <v>274.8</v>
       </c>
       <c r="B54" t="n">
-        <v>104.1</v>
+        <v>137.66</v>
       </c>
       <c r="C54" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="D54" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E54" t="n">
-        <v>11680.86209208304</v>
+        <v>12099.06419045289</v>
       </c>
       <c r="F54" t="n">
-        <v>256.9764554785472</v>
+        <v>220.2760197631337</v>
       </c>
       <c r="G54" t="n">
         <v>1400</v>
       </c>
       <c r="H54" t="n">
-        <v>11507.29586146153</v>
+        <v>12150.90010406196</v>
       </c>
       <c r="I54" t="n">
-        <v>-364.6679283839973</v>
+        <v>-397.0214117561568</v>
       </c>
       <c r="J54" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K54" t="n">
-        <v>1.399999999999999</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254.4</v>
+        <v>274.8</v>
       </c>
       <c r="B55" t="n">
-        <v>105.1</v>
+        <v>138.44</v>
       </c>
       <c r="C55" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="D55" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="E55" t="n">
-        <v>11666.49101686936</v>
+        <v>12099.62550142596</v>
       </c>
       <c r="F55" t="n">
-        <v>205.5050479088804</v>
+        <v>213.5915456632881</v>
       </c>
       <c r="G55" t="n">
         <v>1400</v>
       </c>
       <c r="H55" t="n">
-        <v>11502.56287261871</v>
+        <v>12151.75512426513</v>
       </c>
       <c r="I55" t="n">
-        <v>-381.619589559636</v>
+        <v>-407.2035757919681</v>
       </c>
       <c r="J55" t="n">
-        <v>1235.164</v>
+        <v>1300.775</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6000000000000014</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254.4</v>
+        <v>276.4</v>
       </c>
       <c r="B56" t="n">
-        <v>106.1</v>
+        <v>132.2</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E56" t="n">
-        <v>11686.14367735992</v>
+        <v>12135.57297410662</v>
       </c>
       <c r="F56" t="n">
-        <v>275.8929682904532</v>
+        <v>191.3397060001164</v>
       </c>
       <c r="G56" t="n">
         <v>1400</v>
       </c>
       <c r="H56" t="n">
-        <v>11509.24284096279</v>
+        <v>12201.88584187616</v>
       </c>
       <c r="I56" t="n">
-        <v>-357.6946314003823</v>
+        <v>-399.8528291085224</v>
       </c>
       <c r="J56" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6000000000000014</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>256</v>
+        <v>276.4</v>
       </c>
       <c r="B57" t="n">
-        <v>102.1</v>
+        <v>132.98</v>
       </c>
       <c r="C57" t="n">
-        <v>12.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="E57" t="n">
-        <v>11698.65724840314</v>
+        <v>12136.37287516413</v>
       </c>
       <c r="F57" t="n">
-        <v>191.3802374360935</v>
+        <v>184.2084274122199</v>
       </c>
       <c r="G57" t="n">
         <v>1400</v>
       </c>
       <c r="H57" t="n">
-        <v>11555.39594026693</v>
+        <v>12203.07699888572</v>
       </c>
       <c r="I57" t="n">
-        <v>-383.2094857500261</v>
+        <v>-410.4722330926726</v>
       </c>
       <c r="J57" t="n">
-        <v>1235.164</v>
+        <v>1300.775</v>
       </c>
       <c r="K57" t="n">
-        <v>1.400000000000002</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>256</v>
+        <v>276.4</v>
       </c>
       <c r="B58" t="n">
-        <v>104.1</v>
+        <v>136.88</v>
       </c>
       <c r="C58" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="D58" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="E58" t="n">
-        <v>11702.82798188328</v>
+        <v>12131.21765998745</v>
       </c>
       <c r="F58" t="n">
-        <v>208.1081357570915</v>
+        <v>230.1682061375591</v>
       </c>
       <c r="G58" t="n">
         <v>1400</v>
       </c>
       <c r="H58" t="n">
-        <v>11556.76037975811</v>
+        <v>12199.87806346926</v>
       </c>
       <c r="I58" t="n">
-        <v>-377.7370178538297</v>
+        <v>-381.9530813486019</v>
       </c>
       <c r="J58" t="n">
-        <v>1235.164</v>
+        <v>1300.775</v>
       </c>
       <c r="K58" t="n">
-        <v>2.200000000000003</v>
+        <v>1.9</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>256</v>
+        <v>276.4</v>
       </c>
       <c r="B59" t="n">
-        <v>106.1</v>
+        <v>137.66</v>
       </c>
       <c r="C59" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="D59" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="E59" t="n">
-        <v>11707.38579039638</v>
+        <v>12131.96539358469</v>
       </c>
       <c r="F59" t="n">
-        <v>226.3885072401313</v>
+        <v>223.5020109358297</v>
       </c>
       <c r="G59" t="n">
         <v>1400</v>
       </c>
       <c r="H59" t="n">
-        <v>11558.51189428225</v>
+        <v>12201.01705301855</v>
       </c>
       <c r="I59" t="n">
-        <v>-370.7120767955913</v>
+        <v>-392.107401946585</v>
       </c>
       <c r="J59" t="n">
-        <v>1235.164</v>
+        <v>1300.775</v>
       </c>
       <c r="K59" t="n">
-        <v>1.399999999999999</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>248</v>
+        <v>276.4</v>
       </c>
       <c r="B60" t="n">
-        <v>129.1</v>
+        <v>138.44</v>
       </c>
       <c r="C60" t="n">
         <v>8.6</v>
       </c>
       <c r="D60" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E60" t="n">
-        <v>11584.08928359405</v>
+        <v>12132.71312718193</v>
       </c>
       <c r="F60" t="n">
-        <v>370.584853628679</v>
+        <v>216.8358157341004</v>
       </c>
       <c r="G60" t="n">
         <v>1400</v>
       </c>
       <c r="H60" t="n">
-        <v>11284.24667409208</v>
+        <v>12202.15604256783</v>
       </c>
       <c r="I60" t="n">
-        <v>-371.551647243669</v>
+        <v>-402.261722544568</v>
       </c>
       <c r="J60" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K60" t="n">
-        <v>2.600000000000001</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>248</v>
+        <v>276.4</v>
       </c>
       <c r="B61" t="n">
-        <v>130.1</v>
+        <v>139.22</v>
       </c>
       <c r="C61" t="n">
         <v>8.6</v>
       </c>
       <c r="D61" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E61" t="n">
-        <v>11580.86766689067</v>
+        <v>12133.46086077917</v>
       </c>
       <c r="F61" t="n">
-        <v>362.6110724794044</v>
+        <v>210.169620532371</v>
       </c>
       <c r="G61" t="n">
         <v>1400</v>
       </c>
       <c r="H61" t="n">
-        <v>11278.70249650953</v>
+        <v>12203.29503211711</v>
       </c>
       <c r="I61" t="n">
-        <v>-385.2739682912577</v>
+        <v>-412.4160431425511</v>
       </c>
       <c r="J61" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.6999999999999993</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B62" t="n">
-        <v>131.1</v>
+        <v>132.2</v>
       </c>
       <c r="C62" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E62" t="n">
-        <v>11597.29041994603</v>
+        <v>12169.26789231167</v>
       </c>
       <c r="F62" t="n">
-        <v>403.2588126636124</v>
+        <v>195.5963640737527</v>
       </c>
       <c r="G62" t="n">
         <v>1400</v>
       </c>
       <c r="H62" t="n">
-        <v>11292.8026886857</v>
+        <v>12252.06197007281</v>
       </c>
       <c r="I62" t="n">
-        <v>-350.3747680053635</v>
+        <v>-393.5141100206074</v>
       </c>
       <c r="J62" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1999999999999993</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B63" t="n">
-        <v>132.1</v>
+        <v>132.98</v>
       </c>
       <c r="C63" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E63" t="n">
-        <v>11594.21864588002</v>
+        <v>12170.26659848416</v>
       </c>
       <c r="F63" t="n">
-        <v>395.6559050561648</v>
+        <v>188.4902004124631</v>
       </c>
       <c r="G63" t="n">
         <v>1400</v>
       </c>
       <c r="H63" t="n">
-        <v>11287.40835374051</v>
+        <v>12253.54917382967</v>
       </c>
       <c r="I63" t="n">
-        <v>-363.7262155111252</v>
+        <v>-404.09611460318</v>
       </c>
       <c r="J63" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K63" t="n">
-        <v>3.399999999999999</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B64" t="n">
-        <v>133.1</v>
+        <v>137.66</v>
       </c>
       <c r="C64" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D64" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E64" t="n">
-        <v>11591.14687181401</v>
+        <v>12164.7636940722</v>
       </c>
       <c r="F64" t="n">
-        <v>388.0529974487172</v>
+        <v>227.6453998505049</v>
       </c>
       <c r="G64" t="n">
         <v>1400</v>
       </c>
       <c r="H64" t="n">
-        <v>11282.01401879533</v>
+        <v>12250.97725492393</v>
       </c>
       <c r="I64" t="n">
-        <v>-377.077663016887</v>
+        <v>-385.7959606928357</v>
       </c>
       <c r="J64" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K64" t="n">
-        <v>1.699999999999999</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="B65" t="n">
-        <v>134.1</v>
+        <v>138.44</v>
       </c>
       <c r="C65" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="D65" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="E65" t="n">
-        <v>11628.26289308965</v>
+        <v>12165.69726723344</v>
       </c>
       <c r="F65" t="n">
-        <v>479.9183737591942</v>
+        <v>221.0026816453862</v>
       </c>
       <c r="G65" t="n">
         <v>1400</v>
       </c>
       <c r="H65" t="n">
-        <v>11296.71358152097</v>
+        <v>12252.39932566954</v>
       </c>
       <c r="I65" t="n">
-        <v>-340.6949685636865</v>
+        <v>-395.9145198192372</v>
       </c>
       <c r="J65" t="n">
-        <v>1186.556</v>
+        <v>1300.775</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>249.6</v>
+        <v>278</v>
       </c>
       <c r="B66" t="n">
-        <v>130.1</v>
+        <v>139.22</v>
       </c>
       <c r="C66" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D66" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="E66" t="n">
-        <v>11628.13636847614</v>
+        <v>12166.63084039468</v>
       </c>
       <c r="F66" t="n">
-        <v>400.0888279702605</v>
+        <v>214.3599634402676</v>
       </c>
       <c r="G66" t="n">
         <v>1400</v>
       </c>
       <c r="H66" t="n">
-        <v>11346.97118366542</v>
+        <v>12253.82139641515</v>
       </c>
       <c r="I66" t="n">
-        <v>-355.9415703936889</v>
+        <v>-406.0330789456389</v>
       </c>
       <c r="J66" t="n">
-        <v>1211.644</v>
+        <v>1300.775</v>
       </c>
       <c r="K66" t="n">
-        <v>3.400000000000002</v>
+        <v>1.900000000000002</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>249.6</v>
+        <v>244</v>
       </c>
       <c r="B67" t="n">
-        <v>131.1</v>
+        <v>102.6</v>
       </c>
       <c r="C67" t="n">
-        <v>8.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="D67" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E67" t="n">
-        <v>11625.2780776881</v>
+        <v>11433.29131627695</v>
       </c>
       <c r="F67" t="n">
-        <v>392.403115656427</v>
+        <v>238.0750087062893</v>
       </c>
       <c r="G67" t="n">
         <v>1400</v>
       </c>
       <c r="H67" t="n">
-        <v>11341.95174618398</v>
+        <v>11140.94159848331</v>
       </c>
       <c r="I67" t="n">
-        <v>-369.4384310423721</v>
+        <v>-361.3307407706252</v>
       </c>
       <c r="J67" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K67" t="n">
-        <v>3.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>249.6</v>
+        <v>244</v>
       </c>
       <c r="B68" t="n">
-        <v>133.1</v>
+        <v>103.6</v>
       </c>
       <c r="C68" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="D68" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E68" t="n">
-        <v>11638.11947191144</v>
+        <v>11427.76783982741</v>
       </c>
       <c r="F68" t="n">
-        <v>426.9325841493081</v>
+        <v>226.7502037229197</v>
       </c>
       <c r="G68" t="n">
         <v>1400</v>
       </c>
       <c r="H68" t="n">
-        <v>11350.47084702053</v>
+        <v>11132.56870957964</v>
       </c>
       <c r="I68" t="n">
-        <v>-346.5312592191906</v>
+        <v>-378.4977070549395</v>
       </c>
       <c r="J68" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K68" t="n">
-        <v>2.400000000000002</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>249.6</v>
+        <v>244</v>
       </c>
       <c r="B69" t="n">
-        <v>134.1</v>
+        <v>106.6</v>
       </c>
       <c r="C69" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E69" t="n">
-        <v>11635.40060994233</v>
+        <v>11439.23562902741</v>
       </c>
       <c r="F69" t="n">
-        <v>419.6217846312713</v>
+        <v>250.2626559741059</v>
       </c>
       <c r="G69" t="n">
         <v>1400</v>
       </c>
       <c r="H69" t="n">
-        <v>11345.59083835802</v>
+        <v>11135.48826141726</v>
       </c>
       <c r="I69" t="n">
-        <v>-359.6532070720771</v>
+        <v>-372.5117387065867</v>
       </c>
       <c r="J69" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K69" t="n">
-        <v>3.600000000000001</v>
+        <v>1.100000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>251.2</v>
+        <v>245.6</v>
       </c>
       <c r="B70" t="n">
-        <v>129.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>8.199999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="D70" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E70" t="n">
-        <v>11658.84308971508</v>
+        <v>11462.33632249476</v>
       </c>
       <c r="F70" t="n">
-        <v>397.8581602563216</v>
+        <v>214.7270017875446</v>
       </c>
       <c r="G70" t="n">
         <v>1400</v>
       </c>
       <c r="H70" t="n">
-        <v>11400.89518193867</v>
+        <v>11197.57769342021</v>
       </c>
       <c r="I70" t="n">
-        <v>-359.8588405254839</v>
+        <v>-368.9301564231341</v>
       </c>
       <c r="J70" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K70" t="n">
-        <v>3.5</v>
+        <v>2.100000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>251.2</v>
+        <v>245.6</v>
       </c>
       <c r="B71" t="n">
-        <v>130.1</v>
+        <v>101.6</v>
       </c>
       <c r="C71" t="n">
-        <v>8.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="D71" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E71" t="n">
-        <v>11656.20051101419</v>
+        <v>11471.16023311581</v>
       </c>
       <c r="F71" t="n">
-        <v>390.095636323373</v>
+        <v>234.1792047823644</v>
       </c>
       <c r="G71" t="n">
         <v>1400</v>
       </c>
       <c r="H71" t="n">
-        <v>11396.25455592735</v>
+        <v>11198.34606765969</v>
       </c>
       <c r="I71" t="n">
-        <v>-373.4905898711498</v>
+        <v>-367.236284814035</v>
       </c>
       <c r="J71" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1000000000000014</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>251.2</v>
+        <v>245.6</v>
       </c>
       <c r="B72" t="n">
-        <v>132.1</v>
+        <v>104.6</v>
       </c>
       <c r="C72" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E72" t="n">
-        <v>11667.94387294839</v>
+        <v>11481.47131968423</v>
       </c>
       <c r="F72" t="n">
-        <v>424.5915353619889</v>
+        <v>256.9098689560867</v>
       </c>
       <c r="G72" t="n">
         <v>1400</v>
       </c>
       <c r="H72" t="n">
-        <v>11404.00182324069</v>
+        <v>11200.60161784653</v>
       </c>
       <c r="I72" t="n">
-        <v>-350.7331416579686</v>
+        <v>-362.2639520260331</v>
       </c>
       <c r="J72" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K72" t="n">
-        <v>3.600000000000001</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>251.2</v>
+        <v>245.6</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1</v>
+        <v>105.6</v>
       </c>
       <c r="C73" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E73" t="n">
-        <v>11665.43020052559</v>
+        <v>11476.51406652634</v>
       </c>
       <c r="F73" t="n">
-        <v>417.2076711330865</v>
+        <v>245.9816650264127</v>
       </c>
       <c r="G73" t="n">
         <v>1400</v>
       </c>
       <c r="H73" t="n">
-        <v>11399.49010350747</v>
+        <v>11192.95918589478</v>
       </c>
       <c r="I73" t="n">
-        <v>-363.9862312995884</v>
+        <v>-379.1115997509472</v>
       </c>
       <c r="J73" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K73" t="n">
-        <v>2.900000000000002</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>251.2</v>
+        <v>245.6</v>
       </c>
       <c r="B74" t="n">
-        <v>134.1</v>
+        <v>107.6</v>
       </c>
       <c r="C74" t="n">
-        <v>8.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D74" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E74" t="n">
-        <v>11645.63019621062</v>
+        <v>11493.26958220002</v>
       </c>
       <c r="F74" t="n">
-        <v>359.0455405915782</v>
+        <v>282.918994308711</v>
       </c>
       <c r="G74" t="n">
         <v>1400</v>
       </c>
       <c r="H74" t="n">
-        <v>11394.97838377424</v>
+        <v>11204.34434398074</v>
       </c>
       <c r="I74" t="n">
-        <v>-377.2393209412081</v>
+        <v>-354.013158059129</v>
       </c>
       <c r="J74" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7000000000000028</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>252.8</v>
+        <v>245.6</v>
       </c>
       <c r="B75" t="n">
-        <v>129.1</v>
+        <v>108.6</v>
       </c>
       <c r="C75" t="n">
-        <v>8.6</v>
+        <v>11.4</v>
       </c>
       <c r="D75" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E75" t="n">
-        <v>11671.6871803581</v>
+        <v>11488.56019170002</v>
       </c>
       <c r="F75" t="n">
-        <v>339.3926456700469</v>
+        <v>272.5372005755205</v>
       </c>
       <c r="G75" t="n">
         <v>1400</v>
       </c>
       <c r="H75" t="n">
-        <v>11450.26690664611</v>
+        <v>11196.94977468688</v>
       </c>
       <c r="I75" t="n">
-        <v>-375.9006863199213</v>
+        <v>-370.3143955875597</v>
       </c>
       <c r="J75" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K75" t="n">
-        <v>1.899999999999999</v>
+        <v>2.400000000000002</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B76" t="n">
-        <v>130.1</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C76" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="D76" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E76" t="n">
-        <v>11699.9213849763</v>
+        <v>11513.68343962607</v>
       </c>
       <c r="F76" t="n">
-        <v>430.6026236854882</v>
+        <v>243.0986192824957</v>
       </c>
       <c r="G76" t="n">
         <v>1400</v>
       </c>
       <c r="H76" t="n">
-        <v>11461.39735764977</v>
+        <v>11262.80584895698</v>
       </c>
       <c r="I76" t="n">
-        <v>-339.9440087696366</v>
+        <v>-353.7155850558995</v>
       </c>
       <c r="J76" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3000000000000007</v>
+        <v>1.100000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B77" t="n">
-        <v>130.1</v>
+        <v>100.6</v>
       </c>
       <c r="C77" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D77" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E77" t="n">
-        <v>11669.14409112772</v>
+        <v>11508.80074323677</v>
       </c>
       <c r="F77" t="n">
-        <v>331.1772517557947</v>
+        <v>231.4831435724805</v>
       </c>
       <c r="G77" t="n">
         <v>1400</v>
       </c>
       <c r="H77" t="n">
-        <v>11446.00871072548</v>
+        <v>11255.40430125574</v>
       </c>
       <c r="I77" t="n">
-        <v>-389.6566947344832</v>
+        <v>-371.3231712512401</v>
       </c>
       <c r="J77" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K77" t="n">
-        <v>0.09999999999999787</v>
+        <v>2.700000000000003</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B78" t="n">
-        <v>131.1</v>
+        <v>102.6</v>
       </c>
       <c r="C78" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E78" t="n">
-        <v>11697.61486218596</v>
+        <v>11522.89080996017</v>
       </c>
       <c r="F78" t="n">
-        <v>423.1514524609339</v>
+        <v>265.0020877642385</v>
       </c>
       <c r="G78" t="n">
         <v>1400</v>
       </c>
       <c r="H78" t="n">
-        <v>11457.25744494916</v>
+        <v>11264.45666535526</v>
       </c>
       <c r="I78" t="n">
-        <v>-353.3179058393494</v>
+        <v>-349.7884480301324</v>
       </c>
       <c r="J78" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K78" t="n">
-        <v>2.900000000000002</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B79" t="n">
-        <v>132.1</v>
+        <v>103.6</v>
       </c>
       <c r="C79" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="D79" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E79" t="n">
-        <v>11679.68312603129</v>
+        <v>11518.24062292275</v>
       </c>
       <c r="F79" t="n">
-        <v>365.2233725818351</v>
+        <v>253.9397299451762</v>
       </c>
       <c r="G79" t="n">
         <v>1400</v>
       </c>
       <c r="H79" t="n">
-        <v>11453.11753224854</v>
+        <v>11257.2876270059</v>
       </c>
       <c r="I79" t="n">
-        <v>-366.6918029090622</v>
+        <v>-366.8429163345201</v>
       </c>
       <c r="J79" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6999999999999993</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B80" t="n">
-        <v>133.1</v>
+        <v>106.6</v>
       </c>
       <c r="C80" t="n">
-        <v>8.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D80" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E80" t="n">
-        <v>11677.25832002093</v>
+        <v>11529.07555871995</v>
       </c>
       <c r="F80" t="n">
-        <v>357.390090012432</v>
+        <v>279.715023663591</v>
       </c>
       <c r="G80" t="n">
         <v>1400</v>
       </c>
       <c r="H80" t="n">
-        <v>11448.97761954792</v>
+        <v>11260.56600886728</v>
       </c>
       <c r="I80" t="n">
-        <v>-380.0656999787749</v>
+        <v>-359.0439540720807</v>
       </c>
       <c r="J80" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K80" t="n">
-        <v>1.699999999999999</v>
+        <v>3.099999999999998</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>252.8</v>
+        <v>247.2</v>
       </c>
       <c r="B81" t="n">
-        <v>134.1</v>
+        <v>107.6</v>
       </c>
       <c r="C81" t="n">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
       <c r="D81" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E81" t="n">
-        <v>11706.55707361929</v>
+        <v>11524.65788103439</v>
       </c>
       <c r="F81" t="n">
-        <v>452.0390701315134</v>
+        <v>269.2057837354819</v>
       </c>
       <c r="G81" t="n">
         <v>1400</v>
       </c>
       <c r="H81" t="n">
-        <v>11460.69948665167</v>
+        <v>11253.62947986979</v>
       </c>
       <c r="I81" t="n">
-        <v>-342.1984657042457</v>
+        <v>-375.5453044855151</v>
       </c>
       <c r="J81" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K81" t="n">
-        <v>1.199999999999999</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254.4</v>
+        <v>248.8</v>
       </c>
       <c r="B82" t="n">
-        <v>129.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C82" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="D82" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E82" t="n">
-        <v>11701.42907996369</v>
+        <v>11550.73209911281</v>
       </c>
       <c r="F82" t="n">
-        <v>330.6391285872321</v>
+        <v>241.7182023218966</v>
       </c>
       <c r="G82" t="n">
         <v>1400</v>
       </c>
       <c r="H82" t="n">
-        <v>11500.0672966834</v>
+        <v>11318.9669121472</v>
       </c>
       <c r="I82" t="n">
-        <v>-390.5577381795182</v>
+        <v>-355.8081218771252</v>
       </c>
       <c r="J82" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6000000000000014</v>
+        <v>0.6999999999999993</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>254.4</v>
+        <v>248.8</v>
       </c>
       <c r="B83" t="n">
-        <v>130.1</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C83" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="D83" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E83" t="n">
-        <v>11727.10554443604</v>
+        <v>11546.17562952978</v>
       </c>
       <c r="F83" t="n">
-        <v>422.6018904650725</v>
+        <v>229.9709224265812</v>
       </c>
       <c r="G83" t="n">
         <v>1400</v>
       </c>
       <c r="H83" t="n">
-        <v>11510.18943873136</v>
+        <v>11312.05988285863</v>
       </c>
       <c r="I83" t="n">
-        <v>-354.3042991652545</v>
+        <v>-373.6155064803414</v>
       </c>
       <c r="J83" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K83" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254.4</v>
+        <v>248.8</v>
       </c>
       <c r="B84" t="n">
-        <v>131.1</v>
+        <v>101.6</v>
       </c>
       <c r="C84" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="D84" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E84" t="n">
-        <v>11710.90581444218</v>
+        <v>11559.10732415591</v>
       </c>
       <c r="F84" t="n">
-        <v>364.5809774411816</v>
+        <v>263.3108215580478</v>
       </c>
       <c r="G84" t="n">
         <v>1400</v>
       </c>
       <c r="H84" t="n">
-        <v>11506.42456124274</v>
+        <v>11320.2904580737</v>
       </c>
       <c r="I84" t="n">
-        <v>-367.7885751004217</v>
+        <v>-352.3958167646764</v>
       </c>
       <c r="J84" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K84" t="n">
-        <v>2.900000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>254.4</v>
+        <v>248.8</v>
       </c>
       <c r="B85" t="n">
-        <v>132.1</v>
+        <v>102.6</v>
       </c>
       <c r="C85" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E85" t="n">
-        <v>11708.70067191313</v>
+        <v>11554.76782931493</v>
       </c>
       <c r="F85" t="n">
-        <v>356.6830443934409</v>
+        <v>252.1229359434617</v>
       </c>
       <c r="G85" t="n">
         <v>1400</v>
       </c>
       <c r="H85" t="n">
-        <v>11502.65968375413</v>
+        <v>11313.60040352718</v>
       </c>
       <c r="I85" t="n">
-        <v>-381.2728510355888</v>
+        <v>-369.6438070871633</v>
       </c>
       <c r="J85" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K85" t="n">
-        <v>2.300000000000001</v>
+        <v>2.099999999999998</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>254.4</v>
+        <v>248.8</v>
       </c>
       <c r="B86" t="n">
-        <v>133.1</v>
+        <v>105.6</v>
       </c>
       <c r="C86" t="n">
-        <v>7.4</v>
+        <v>11.4</v>
       </c>
       <c r="D86" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E86" t="n">
-        <v>11735.1301118832</v>
+        <v>11564.66187755237</v>
       </c>
       <c r="F86" t="n">
-        <v>451.3426614583146</v>
+        <v>277.631315144718</v>
       </c>
       <c r="G86" t="n">
         <v>1400</v>
       </c>
       <c r="H86" t="n">
-        <v>11513.21209751507</v>
+        <v>11316.44277264802</v>
       </c>
       <c r="I86" t="n">
-        <v>-343.4783519144488</v>
+        <v>-362.3157420096093</v>
       </c>
       <c r="J86" t="n">
-        <v>1211.644</v>
+        <v>1192.975</v>
       </c>
       <c r="K86" t="n">
-        <v>0.2999999999999989</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>256</v>
+        <v>248.8</v>
       </c>
       <c r="B87" t="n">
-        <v>130.1</v>
+        <v>108.6</v>
       </c>
       <c r="C87" t="n">
-        <v>8.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D87" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E87" t="n">
-        <v>11741.91288333636</v>
+        <v>11575.85777424211</v>
       </c>
       <c r="F87" t="n">
-        <v>364.8691132942415</v>
+        <v>306.4960600303502</v>
       </c>
       <c r="G87" t="n">
         <v>1400</v>
       </c>
       <c r="H87" t="n">
-        <v>11559.36345935476</v>
+        <v>11320.58699022117</v>
       </c>
       <c r="I87" t="n">
-        <v>-367.2966358391</v>
+        <v>-351.6313112476797</v>
       </c>
       <c r="J87" t="n">
-        <v>1235.164</v>
+        <v>1192.975</v>
       </c>
       <c r="K87" t="n">
-        <v>3.5</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>256</v>
+        <v>250.4</v>
       </c>
       <c r="B88" t="n">
-        <v>131.1</v>
+        <v>108.6</v>
       </c>
       <c r="C88" t="n">
-        <v>8.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D88" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>11739.92912379244</v>
+        <v>11584.69753858639</v>
       </c>
       <c r="F88" t="n">
-        <v>356.9126883387785</v>
+        <v>233.6951911512153</v>
       </c>
       <c r="G88" t="n">
         <v>1400</v>
       </c>
       <c r="H88" t="n">
-        <v>11555.97655281637</v>
+        <v>11366.11729573713</v>
       </c>
       <c r="I88" t="n">
-        <v>-380.8807760069637</v>
+        <v>-380.149445084987</v>
       </c>
       <c r="J88" t="n">
-        <v>1235.164</v>
+        <v>1223.6</v>
       </c>
       <c r="K88" t="n">
-        <v>2.900000000000002</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B89" t="n">
-        <v>133.1</v>
+        <v>100.6</v>
       </c>
       <c r="C89" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="D89" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>11748.84152642634</v>
+        <v>11608.30241861009</v>
       </c>
       <c r="F89" t="n">
-        <v>392.658382894786</v>
+        <v>194.4788022049154</v>
       </c>
       <c r="G89" t="n">
         <v>1400</v>
       </c>
       <c r="H89" t="n">
-        <v>11562.08266146131</v>
+        <v>11421.77976080537</v>
       </c>
       <c r="I89" t="n">
-        <v>-356.3905118757577</v>
+        <v>-379.5789110308394</v>
       </c>
       <c r="J89" t="n">
-        <v>1235.164</v>
+        <v>1223.6</v>
       </c>
       <c r="K89" t="n">
-        <v>2.300000000000001</v>
+        <v>0.6999999999999993</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B90" t="n">
-        <v>134.1</v>
+        <v>103.6</v>
       </c>
       <c r="C90" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>11746.95453564066</v>
+        <v>11615.83007259307</v>
       </c>
       <c r="F90" t="n">
-        <v>385.0900762298332</v>
+        <v>217.6465389418652</v>
       </c>
       <c r="G90" t="n">
         <v>1400</v>
       </c>
       <c r="H90" t="n">
-        <v>11558.79252368115</v>
+        <v>11423.7451088896</v>
       </c>
       <c r="I90" t="n">
-        <v>-369.5865337531112</v>
+        <v>-373.5301915872022</v>
       </c>
       <c r="J90" t="n">
-        <v>1235.164</v>
+        <v>1223.6</v>
       </c>
       <c r="K90" t="n">
-        <v>3.600000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="B91" t="n">
-        <v>103.9</v>
+        <v>107.6</v>
       </c>
       <c r="C91" t="n">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="D91" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>11911.57808901142</v>
+        <v>11620.94739401992</v>
       </c>
       <c r="F91" t="n">
-        <v>135.5077611716522</v>
+        <v>233.396034851713</v>
       </c>
       <c r="G91" t="n">
         <v>1400</v>
       </c>
       <c r="H91" t="n">
-        <v>11873.89006137695</v>
+        <v>11421.44602245145</v>
       </c>
       <c r="I91" t="n">
-        <v>-403.4561439027256</v>
+        <v>-380.6060520684379</v>
       </c>
       <c r="J91" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1999999999999993</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>266</v>
+        <v>253.6</v>
       </c>
       <c r="B92" t="n">
-        <v>104.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C92" t="n">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
       <c r="D92" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>11916.58102330835</v>
+        <v>11645.67276532046</v>
       </c>
       <c r="F92" t="n">
-        <v>207.0530548562865</v>
+        <v>196.0993345112095</v>
       </c>
       <c r="G92" t="n">
         <v>1400</v>
       </c>
       <c r="H92" t="n">
-        <v>11875.6032803721</v>
+        <v>11476.94551071116</v>
       </c>
       <c r="I92" t="n">
-        <v>-378.9559708283446</v>
+        <v>-377.1866966739291</v>
       </c>
       <c r="J92" t="n">
-        <v>1246.336</v>
+        <v>1223.6</v>
       </c>
       <c r="K92" t="n">
-        <v>0.5</v>
+        <v>2.199999999999999</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>266</v>
+        <v>253.6</v>
       </c>
       <c r="B93" t="n">
-        <v>105.9</v>
+        <v>102.6</v>
       </c>
       <c r="C93" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>11912.83091527987</v>
+        <v>11652.38119833505</v>
       </c>
       <c r="F93" t="n">
-        <v>153.4240115143184</v>
+        <v>218.8926345462812</v>
       </c>
       <c r="G93" t="n">
         <v>1400</v>
       </c>
       <c r="H93" t="n">
-        <v>11874.41742031845</v>
+        <v>11478.57179750257</v>
       </c>
       <c r="I93" t="n">
-        <v>-395.9145596827615</v>
+        <v>-371.6610481805782</v>
       </c>
       <c r="J93" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K93" t="n">
-        <v>1.399999999999999</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>266</v>
+        <v>253.6</v>
       </c>
       <c r="B94" t="n">
-        <v>107.9</v>
+        <v>103.6</v>
       </c>
       <c r="C94" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="D94" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>11914.1953519063</v>
+        <v>11648.99310085294</v>
       </c>
       <c r="F94" t="n">
-        <v>172.9363643374006</v>
+        <v>207.3808668518006</v>
       </c>
       <c r="G94" t="n">
         <v>1400</v>
       </c>
       <c r="H94" t="n">
-        <v>11875.05638961795</v>
+        <v>11473.4896512794</v>
       </c>
       <c r="I94" t="n">
-        <v>-386.7768729823816</v>
+        <v>-388.928699722299</v>
       </c>
       <c r="J94" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K94" t="n">
-        <v>2.5</v>
+        <v>0.6999999999999993</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>266</v>
+        <v>253.6</v>
       </c>
       <c r="B95" t="n">
-        <v>108.9</v>
+        <v>105.6</v>
       </c>
       <c r="C95" t="n">
         <v>11.4</v>
       </c>
       <c r="D95" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>11913.40012810562</v>
+        <v>11660.10606059427</v>
       </c>
       <c r="F95" t="n">
-        <v>161.5641341644387</v>
+        <v>245.1394648896971</v>
       </c>
       <c r="G95" t="n">
         <v>1400</v>
       </c>
       <c r="H95" t="n">
-        <v>11873.89843215379</v>
+        <v>11481.21451353863</v>
       </c>
       <c r="I95" t="n">
-        <v>-403.3364362166948</v>
+        <v>-362.6818693788831</v>
       </c>
       <c r="J95" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K95" t="n">
-        <v>0.3999999999999986</v>
+        <v>1.5</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>267.6</v>
+        <v>253.6</v>
       </c>
       <c r="B96" t="n">
-        <v>103.9</v>
+        <v>106.6</v>
       </c>
       <c r="C96" t="n">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="D96" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>11946.91925884594</v>
+        <v>11656.88736798626</v>
       </c>
       <c r="F96" t="n">
-        <v>133.5318830232891</v>
+        <v>234.2032855799405</v>
       </c>
       <c r="G96" t="n">
         <v>1400</v>
       </c>
       <c r="H96" t="n">
-        <v>11924.29468064913</v>
+        <v>11476.30177218956</v>
       </c>
       <c r="I96" t="n">
-        <v>-406.274199622522</v>
+        <v>-379.3739325358802</v>
       </c>
       <c r="J96" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1999999999999993</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>267.6</v>
+        <v>255.2</v>
       </c>
       <c r="B97" t="n">
-        <v>104.9</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>11.8</v>
+        <v>12.6</v>
       </c>
       <c r="D97" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>11948.16547830092</v>
+        <v>11682.64440817089</v>
       </c>
       <c r="F97" t="n">
-        <v>163.2657784470309</v>
+        <v>198.8572949333641</v>
       </c>
       <c r="G97" t="n">
         <v>1400</v>
       </c>
       <c r="H97" t="n">
-        <v>11925.32314670472</v>
+        <v>11531.52269777608</v>
       </c>
       <c r="I97" t="n">
-        <v>-381.7357429152943</v>
+        <v>-373.1154217650342</v>
       </c>
       <c r="J97" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K97" t="n">
-        <v>2.100000000000001</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>267.6</v>
+        <v>255.2</v>
       </c>
       <c r="B98" t="n">
-        <v>105.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>11.8</v>
+        <v>12.6</v>
       </c>
       <c r="D98" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>11947.67134558692</v>
+        <v>11679.4257916209</v>
       </c>
       <c r="F98" t="n">
-        <v>151.4761290518643</v>
+        <v>186.6753202369478</v>
       </c>
       <c r="G98" t="n">
         <v>1400</v>
       </c>
       <c r="H98" t="n">
-        <v>11924.61126059132</v>
+        <v>11526.77140667847</v>
       </c>
       <c r="I98" t="n">
-        <v>-398.720831026975</v>
+        <v>-391.0983367930774</v>
       </c>
       <c r="J98" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K98" t="n">
-        <v>1.699999999999999</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>267.6</v>
+        <v>255.2</v>
       </c>
       <c r="B99" t="n">
-        <v>107.9</v>
+        <v>101.6</v>
       </c>
       <c r="C99" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="D99" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>11948.49043337386</v>
+        <v>11688.56053192468</v>
       </c>
       <c r="F99" t="n">
-        <v>171.0189716085981</v>
+        <v>221.2489246134433</v>
       </c>
       <c r="G99" t="n">
         <v>1400</v>
       </c>
       <c r="H99" t="n">
-        <v>11924.99484157948</v>
+        <v>11532.84079788703</v>
       </c>
       <c r="I99" t="n">
-        <v>-389.5688659032695</v>
+        <v>-368.1266130798351</v>
       </c>
       <c r="J99" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K99" t="n">
-        <v>3.200000000000003</v>
+        <v>2.400000000000002</v>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>267.6</v>
+        <v>255.2</v>
       </c>
       <c r="B100" t="n">
-        <v>108.9</v>
+        <v>102.6</v>
       </c>
       <c r="C100" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="D100" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>11948.01305092135</v>
+        <v>11685.49518282945</v>
       </c>
       <c r="F100" t="n">
-        <v>159.6289713454712</v>
+        <v>209.6470439501898</v>
       </c>
       <c r="G100" t="n">
         <v>1400</v>
       </c>
       <c r="H100" t="n">
-        <v>11924.29970572758</v>
+        <v>11528.24277424418</v>
       </c>
       <c r="I100" t="n">
-        <v>-406.1543048829104</v>
+        <v>-385.5294340747154</v>
       </c>
       <c r="J100" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K100" t="n">
-        <v>0.1999999999999993</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>269.2</v>
+        <v>255.2</v>
       </c>
       <c r="B101" t="n">
-        <v>103.9</v>
+        <v>104.6</v>
       </c>
       <c r="C101" t="n">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="D101" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>11982.30181944571</v>
+        <v>11695.39626040705</v>
       </c>
       <c r="F101" t="n">
-        <v>132.5435586162862</v>
+        <v>247.1211184924985</v>
       </c>
       <c r="G101" t="n">
         <v>1400</v>
       </c>
       <c r="H101" t="n">
-        <v>11974.75833265207</v>
+        <v>11535.07850272654</v>
       </c>
       <c r="I101" t="n">
-        <v>-407.6837770554607</v>
+        <v>-359.6572401956601</v>
       </c>
       <c r="J101" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K101" t="n">
-        <v>0.09999999999999787</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>269.2</v>
+        <v>255.2</v>
       </c>
       <c r="B102" t="n">
-        <v>104.9</v>
+        <v>105.6</v>
       </c>
       <c r="C102" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="D102" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>11982.7173339326</v>
+        <v>11692.48417876658</v>
       </c>
       <c r="F102" t="n">
-        <v>162.3006577308029</v>
+        <v>236.0993318624078</v>
       </c>
       <c r="G102" t="n">
         <v>1400</v>
       </c>
       <c r="H102" t="n">
-        <v>11975.1012438012</v>
+        <v>11530.63374653846</v>
       </c>
       <c r="I102" t="n">
-        <v>-383.1261710657924</v>
+        <v>-376.4799671573775</v>
       </c>
       <c r="J102" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K102" t="n">
-        <v>1.900000000000002</v>
+        <v>3.500000000000004</v>
       </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>269.2</v>
+        <v>255.2</v>
       </c>
       <c r="B103" t="n">
-        <v>105.9</v>
+        <v>108.6</v>
       </c>
       <c r="C103" t="n">
-        <v>11.8</v>
+        <v>10.8</v>
       </c>
       <c r="D103" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>11982.5525802046</v>
+        <v>11700.39277943227</v>
       </c>
       <c r="F103" t="n">
-        <v>150.5018079474933</v>
+        <v>266.0321839736016</v>
       </c>
       <c r="G103" t="n">
         <v>1400</v>
       </c>
       <c r="H103" t="n">
-        <v>11974.86388673544</v>
+        <v>11533.94432356131</v>
       </c>
       <c r="I103" t="n">
-        <v>-400.1245139739503</v>
+        <v>-363.9499360410641</v>
       </c>
       <c r="J103" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K103" t="n">
-        <v>1.899999999999999</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="L103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>269.2</v>
+        <v>256.8</v>
       </c>
       <c r="B104" t="n">
-        <v>106.9</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>11.4</v>
+        <v>12.6</v>
       </c>
       <c r="D104" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>11982.9848493079</v>
+        <v>11716.30601300933</v>
       </c>
       <c r="F104" t="n">
-        <v>181.4587900908211</v>
+        <v>190.4645142265006</v>
       </c>
       <c r="G104" t="n">
         <v>1400</v>
       </c>
       <c r="H104" t="n">
-        <v>11975.22355250097</v>
+        <v>11581.21363825186</v>
       </c>
       <c r="I104" t="n">
-        <v>-374.367024955471</v>
+        <v>-385.5047647132612</v>
       </c>
       <c r="J104" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K104" t="n">
-        <v>0.1999999999999993</v>
+        <v>2.100000000000001</v>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>269.2</v>
+        <v>256.8</v>
       </c>
       <c r="B105" t="n">
-        <v>107.9</v>
+        <v>100.6</v>
       </c>
       <c r="C105" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>11982.82568045203</v>
+        <v>11724.33482960242</v>
       </c>
       <c r="F105" t="n">
-        <v>170.0599013171152</v>
+        <v>224.6955484515211</v>
       </c>
       <c r="G105" t="n">
         <v>1400</v>
       </c>
       <c r="H105" t="n">
-        <v>11974.99178030734</v>
+        <v>11586.50224440362</v>
       </c>
       <c r="I105" t="n">
-        <v>-390.9654068540253</v>
+        <v>-362.9566773227184</v>
       </c>
       <c r="J105" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K105" t="n">
-        <v>3.5</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="L105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>270.8</v>
+        <v>256.8</v>
       </c>
       <c r="B106" t="n">
-        <v>104.9</v>
+        <v>101.6</v>
       </c>
       <c r="C106" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="D106" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E106" t="n">
-        <v>12017.2826660674</v>
+        <v>11721.59461916109</v>
       </c>
       <c r="F106" t="n">
-        <v>162.3006577308029</v>
+        <v>213.0126016170432</v>
       </c>
       <c r="G106" t="n">
         <v>1400</v>
       </c>
       <c r="H106" t="n">
-        <v>12024.8987561988</v>
+        <v>11582.39192874163</v>
       </c>
       <c r="I106" t="n">
-        <v>-383.1261710657924</v>
+        <v>-380.4810975744352</v>
       </c>
       <c r="J106" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>270.8</v>
+        <v>256.8</v>
       </c>
       <c r="B107" t="n">
-        <v>105.9</v>
+        <v>104.6</v>
       </c>
       <c r="C107" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="D107" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>12017.4474197954</v>
+        <v>11727.70528844525</v>
       </c>
       <c r="F107" t="n">
-        <v>150.5018079474933</v>
+        <v>239.0655730579288</v>
       </c>
       <c r="G107" t="n">
         <v>1400</v>
       </c>
       <c r="H107" t="n">
-        <v>12025.13611326456</v>
+        <v>11584.3922823638</v>
       </c>
       <c r="I107" t="n">
-        <v>-400.1245139739503</v>
+        <v>-371.9525463852664</v>
       </c>
       <c r="J107" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K107" t="n">
-        <v>1.300000000000001</v>
+        <v>2.599999999999998</v>
       </c>
       <c r="L107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>270.8</v>
+        <v>256.8</v>
       </c>
       <c r="B108" t="n">
-        <v>105.9</v>
+        <v>107.6</v>
       </c>
       <c r="C108" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D108" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>12018.03885775457</v>
+        <v>11734.63802086181</v>
       </c>
       <c r="F108" t="n">
-        <v>108.1459370304592</v>
+        <v>268.6234285491578</v>
       </c>
       <c r="G108" t="n">
         <v>1400</v>
       </c>
       <c r="H108" t="n">
-        <v>12025.13611326456</v>
+        <v>11587.21469911837</v>
       </c>
       <c r="I108" t="n">
-        <v>-400.1245139739504</v>
+        <v>-359.9191111457545</v>
       </c>
       <c r="J108" t="n">
-        <v>1287.104</v>
+        <v>1223.6</v>
       </c>
       <c r="K108" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>270.8</v>
+        <v>256.8</v>
       </c>
       <c r="B109" t="n">
-        <v>107.9</v>
+        <v>108.6</v>
       </c>
       <c r="C109" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="D109" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>12017.17431954797</v>
+        <v>11732.17183146461</v>
       </c>
       <c r="F109" t="n">
-        <v>170.0599013171152</v>
+        <v>258.1087763981277</v>
       </c>
       <c r="G109" t="n">
         <v>1400</v>
       </c>
       <c r="H109" t="n">
-        <v>12025.00821969266</v>
+        <v>11583.37840450051</v>
       </c>
       <c r="I109" t="n">
-        <v>-390.9654068540253</v>
+        <v>-376.2752367140235</v>
       </c>
       <c r="J109" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K109" t="n">
-        <v>2.300000000000001</v>
+        <v>2.700000000000003</v>
       </c>
       <c r="L109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>272.4</v>
+        <v>258.4</v>
       </c>
       <c r="B110" t="n">
-        <v>103.9</v>
+        <v>100.6</v>
       </c>
       <c r="C110" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D110" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>12054.82109332304</v>
+        <v>11757.25873359259</v>
       </c>
       <c r="F110" t="n">
-        <v>92.00833820438061</v>
+        <v>217.4567586836722</v>
       </c>
       <c r="G110" t="n">
         <v>1400</v>
       </c>
       <c r="H110" t="n">
-        <v>12075.70531935087</v>
+        <v>11635.88810038889</v>
       </c>
       <c r="I110" t="n">
-        <v>-406.274199622522</v>
+        <v>-373.8148619744917</v>
       </c>
       <c r="J110" t="n">
-        <v>1287.104</v>
+        <v>1223.6</v>
       </c>
       <c r="K110" t="n">
-        <v>0.6999999999999993</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>272.4</v>
+        <v>258.4</v>
       </c>
       <c r="B111" t="n">
-        <v>105.9</v>
+        <v>103.6</v>
       </c>
       <c r="C111" t="n">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="D111" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>12054.10250710505</v>
+        <v>11762.51893200977</v>
       </c>
       <c r="F111" t="n">
-        <v>109.1532859688768</v>
+        <v>243.082447213191</v>
       </c>
       <c r="G111" t="n">
         <v>1400</v>
       </c>
       <c r="H111" t="n">
-        <v>12075.38873940868</v>
+        <v>11637.52889622544</v>
       </c>
       <c r="I111" t="n">
-        <v>-398.720831026975</v>
+        <v>-365.8215279377609</v>
       </c>
       <c r="J111" t="n">
-        <v>1287.104</v>
+        <v>1223.6</v>
       </c>
       <c r="K111" t="n">
-        <v>1.700000000000003</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="L111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>272.4</v>
+        <v>258.4</v>
       </c>
       <c r="B112" t="n">
-        <v>107.9</v>
+        <v>107.6</v>
       </c>
       <c r="C112" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="D112" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>12051.50956662614</v>
+        <v>11766.3313693947</v>
       </c>
       <c r="F112" t="n">
-        <v>171.0189716085981</v>
+        <v>261.6551939455944</v>
       </c>
       <c r="G112" t="n">
         <v>1400</v>
       </c>
       <c r="H112" t="n">
-        <v>12075.00515842052</v>
+        <v>11636.51546350286</v>
       </c>
       <c r="I112" t="n">
-        <v>-389.5688659032695</v>
+        <v>-370.7585871957419</v>
       </c>
       <c r="J112" t="n">
-        <v>1267.504</v>
+        <v>1223.6</v>
       </c>
       <c r="K112" t="n">
-        <v>0.6999999999999993</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>272.4</v>
+        <v>260</v>
       </c>
       <c r="B113" t="n">
-        <v>107.9</v>
+        <v>103.6</v>
       </c>
       <c r="C113" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="D113" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E113" t="n">
-        <v>12053.31691984109</v>
+        <v>11784.12058552447</v>
       </c>
       <c r="F113" t="n">
-        <v>127.8968302615315</v>
+        <v>175.687001455223</v>
       </c>
       <c r="G113" t="n">
         <v>1400</v>
       </c>
       <c r="H113" t="n">
-        <v>12075.00515842052</v>
+        <v>11685.17585388985</v>
       </c>
       <c r="I113" t="n">
-        <v>-389.5688659032694</v>
+        <v>-385.4564562111331</v>
       </c>
       <c r="J113" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K113" t="n">
-        <v>1.5</v>
+        <v>0.9000000000000021</v>
       </c>
       <c r="L113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>272.4</v>
+        <v>260</v>
       </c>
       <c r="B114" t="n">
-        <v>108.9</v>
+        <v>107.6</v>
       </c>
       <c r="C114" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="D114" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="E114" t="n">
-        <v>12053.8110525551</v>
+        <v>11786.99619934664</v>
       </c>
       <c r="F114" t="n">
-        <v>116.1071808663648</v>
+        <v>191.9954178451051</v>
       </c>
       <c r="G114" t="n">
         <v>1400</v>
       </c>
       <c r="H114" t="n">
-        <v>12075.70029427242</v>
+        <v>11684.23120780335</v>
       </c>
       <c r="I114" t="n">
-        <v>-406.1543048829105</v>
+        <v>-390.8138103875194</v>
       </c>
       <c r="J114" t="n">
-        <v>1287.104</v>
+        <v>1251.775</v>
       </c>
       <c r="K114" t="n">
-        <v>0.9000000000000021</v>
+        <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B115" t="n">
-        <v>103.9</v>
+        <v>128.6</v>
       </c>
       <c r="C115" t="n">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="D115" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E115" t="n">
-        <v>12091.32099003738</v>
+        <v>11515.17904649715</v>
       </c>
       <c r="F115" t="n">
-        <v>94.0489992428536</v>
+        <v>405.9697365549736</v>
       </c>
       <c r="G115" t="n">
         <v>1400</v>
       </c>
       <c r="H115" t="n">
-        <v>12126.10993862305</v>
+        <v>11148.74460489616</v>
       </c>
       <c r="I115" t="n">
-        <v>-403.4561439027259</v>
+        <v>-345.3322067465</v>
       </c>
       <c r="J115" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K115" t="n">
-        <v>1.899999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="L115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B116" t="n">
-        <v>105.9</v>
+        <v>129.6</v>
       </c>
       <c r="C116" t="n">
-        <v>12.2</v>
+        <v>8.6</v>
       </c>
       <c r="D116" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E116" t="n">
-        <v>12090.12396894794</v>
+        <v>11511.40905463477</v>
       </c>
       <c r="F116" t="n">
-        <v>111.1671983453123</v>
+        <v>398.2401077568007</v>
       </c>
       <c r="G116" t="n">
         <v>1400</v>
       </c>
       <c r="H116" t="n">
-        <v>12125.58257968155</v>
+        <v>11142.12520057965</v>
       </c>
       <c r="I116" t="n">
-        <v>-395.9145596827617</v>
+        <v>-358.9039968456174</v>
       </c>
       <c r="J116" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K116" t="n">
-        <v>2.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B117" t="n">
-        <v>106.9</v>
+        <v>130.6</v>
       </c>
       <c r="C117" t="n">
-        <v>12.2</v>
+        <v>8.6</v>
       </c>
       <c r="D117" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E117" t="n">
-        <v>12090.97499792761</v>
+        <v>11507.63906277238</v>
       </c>
       <c r="F117" t="n">
-        <v>98.99691693214231</v>
+        <v>390.5104789586279</v>
       </c>
       <c r="G117" t="n">
         <v>1400</v>
       </c>
       <c r="H117" t="n">
-        <v>12126.7684397352</v>
+        <v>11135.50579626313</v>
       </c>
       <c r="I117" t="n">
-        <v>-412.8731485371788</v>
+        <v>-372.4757869447348</v>
       </c>
       <c r="J117" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K117" t="n">
-        <v>0.3000000000000007</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="L117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B118" t="n">
-        <v>107.9</v>
+        <v>133.6</v>
       </c>
       <c r="C118" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E118" t="n">
-        <v>12088.81533750049</v>
+        <v>11531.46891831183</v>
       </c>
       <c r="F118" t="n">
-        <v>129.8814999281863</v>
+        <v>439.3689233154505</v>
       </c>
       <c r="G118" t="n">
         <v>1400</v>
       </c>
       <c r="H118" t="n">
-        <v>12124.94361038205</v>
+        <v>11150.7874144402</v>
       </c>
       <c r="I118" t="n">
-        <v>-386.7768729823821</v>
+        <v>-341.1438264907459</v>
       </c>
       <c r="J118" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K118" t="n">
-        <v>1.399999999999999</v>
+        <v>2.100000000000001</v>
       </c>
       <c r="L118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B119" t="n">
-        <v>108.9</v>
+        <v>134.6</v>
       </c>
       <c r="C119" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="D119" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="E119" t="n">
-        <v>12089.63846389068</v>
+        <v>11527.96194913752</v>
       </c>
       <c r="F119" t="n">
-        <v>118.1102441351204</v>
+        <v>432.1785709450572</v>
       </c>
       <c r="G119" t="n">
         <v>1400</v>
       </c>
       <c r="H119" t="n">
-        <v>12126.10156784621</v>
+        <v>11144.43103281176</v>
       </c>
       <c r="I119" t="n">
-        <v>-403.336436216695</v>
+        <v>-354.1763401620838</v>
       </c>
       <c r="J119" t="n">
-        <v>1287.104</v>
+        <v>1192.975</v>
       </c>
       <c r="K119" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>244</v>
+      </c>
+      <c r="B120" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C120" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E120" t="n">
+        <v>11524.45497996321</v>
+      </c>
+      <c r="F120" t="n">
+        <v>424.9882185746638</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H120" t="n">
+        <v>11138.07465118331</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-367.2088538334218</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B121" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="C121" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D121" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>11550.22842098423</v>
+      </c>
+      <c r="F121" t="n">
+        <v>408.4840574606668</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H121" t="n">
+        <v>11210.28478568162</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-340.9175270167362</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B122" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>11546.67572288774</v>
+      </c>
+      <c r="F122" t="n">
+        <v>400.6521779777337</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H122" t="n">
+        <v>11204.04690879127</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-354.6688502949095</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B123" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C123" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E123" t="n">
+        <v>11543.12302479125</v>
+      </c>
+      <c r="F123" t="n">
+        <v>392.8202984948005</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H123" t="n">
+        <v>11197.80903190092</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-368.4201735730829</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1.699999999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B124" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="C124" t="n">
+        <v>8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11565.08365628072</v>
+      </c>
+      <c r="F124" t="n">
+        <v>441.2322419032569</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H124" t="n">
+        <v>11211.71412700881</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-337.766561550347</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2.400000000000002</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B125" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="C125" t="n">
+        <v>8</v>
+      </c>
+      <c r="D125" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>11561.77882084213</v>
+      </c>
+      <c r="F125" t="n">
+        <v>433.9467726168075</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11205.72411277635</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-350.9714746320365</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="B126" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="C126" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>11558.47398540353</v>
+      </c>
+      <c r="F126" t="n">
+        <v>426.661303330358</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H126" t="n">
+        <v>11199.7340985439</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-364.1763877137261</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B127" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>11578.08853009441</v>
+      </c>
+      <c r="F127" t="n">
+        <v>396.3122750765044</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H127" t="n">
+        <v>11259.20195400297</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-362.2889123656726</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B128" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C128" t="n">
+        <v>8</v>
+      </c>
+      <c r="D128" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>11598.22383996646</v>
+      </c>
+      <c r="F128" t="n">
+        <v>444.2122844330428</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H128" t="n">
+        <v>11271.78070993921</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-332.36523446511</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B129" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="C129" t="n">
+        <v>8</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>11595.12371527484</v>
+      </c>
+      <c r="F129" t="n">
+        <v>436.8373792203348</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H129" t="n">
+        <v>11266.16173393565</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-345.7322501631431</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B130" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="C130" t="n">
+        <v>8</v>
+      </c>
+      <c r="D130" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E130" t="n">
+        <v>11592.02359058323</v>
+      </c>
+      <c r="F130" t="n">
+        <v>429.4624740076268</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H130" t="n">
+        <v>11260.5427579321</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-359.0992658611764</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B131" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E131" t="n">
+        <v>11611.1513599305</v>
+      </c>
+      <c r="F131" t="n">
+        <v>474.9656391700352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H131" t="n">
+        <v>11269.59512203162</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-337.564542640069</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>2</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="B132" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>11608.28374459076</v>
+      </c>
+      <c r="F132" t="n">
+        <v>468.1438518482802</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H132" t="n">
+        <v>11264.20865537993</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-350.3784404471494</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B133" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C133" t="n">
+        <v>8</v>
+      </c>
+      <c r="D133" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E133" t="n">
+        <v>11627.96064229954</v>
+      </c>
+      <c r="F133" t="n">
+        <v>440.8252733094812</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H133" t="n">
+        <v>11325.67866416792</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-338.5041921265654</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B134" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>11625.06764573889</v>
+      </c>
+      <c r="F134" t="n">
+        <v>433.3666828997572</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H134" t="n">
+        <v>11320.43510790173</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-352.0228872441901</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B135" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="C135" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" t="n">
+        <v>11593.8377478666</v>
+      </c>
+      <c r="F135" t="n">
+        <v>352.8511994267856</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H135" t="n">
+        <v>11310.46873475027</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-377.7177312056897</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B136" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E136" t="n">
+        <v>11639.80746321543</v>
+      </c>
+      <c r="F136" t="n">
+        <v>471.3682010373014</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H136" t="n">
+        <v>11323.42212685061</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-344.32189264615</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1192.975</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1.700000000000001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B137" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C137" t="n">
+        <v>8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>6</v>
+      </c>
+      <c r="E137" t="n">
+        <v>11607.70966637495</v>
+      </c>
+      <c r="F137" t="n">
+        <v>388.6151404414126</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H137" t="n">
+        <v>11313.49191615616</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-369.923504227528</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="B138" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="C138" t="n">
+        <v>8</v>
+      </c>
+      <c r="D138" t="n">
+        <v>6</v>
+      </c>
+      <c r="E138" t="n">
+        <v>11604.81666981429</v>
+      </c>
+      <c r="F138" t="n">
+        <v>381.1565500316884</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H138" t="n">
+        <v>11308.42917217501</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-382.9760374445452</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="B139" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C139" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D139" t="n">
+        <v>6</v>
+      </c>
+      <c r="E139" t="n">
+        <v>11629.00398191901</v>
+      </c>
+      <c r="F139" t="n">
+        <v>358.1221395153614</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H139" t="n">
+        <v>11370.16955069971</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-368.7693910553166</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="B140" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C140" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6</v>
+      </c>
+      <c r="E140" t="n">
+        <v>11626.11909841916</v>
+      </c>
+      <c r="F140" t="n">
+        <v>350.0204454213908</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H140" t="n">
+        <v>11365.27195778136</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-382.523429866011</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="B141" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="C141" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" t="n">
+        <v>11641.46936225093</v>
+      </c>
+      <c r="F141" t="n">
+        <v>393.1289944609373</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H141" t="n">
+        <v>11372.57138393912</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-362.0242596933597</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="B142" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>6</v>
+      </c>
+      <c r="E142" t="n">
+        <v>11638.78574969292</v>
+      </c>
+      <c r="F142" t="n">
+        <v>385.5925348386389</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H142" t="n">
+        <v>11367.87506196262</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-375.2130640323819</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>250.4</v>
+      </c>
+      <c r="B143" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C143" t="n">
+        <v>8</v>
+      </c>
+      <c r="D143" t="n">
+        <v>6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>11636.10213713492</v>
+      </c>
+      <c r="F143" t="n">
+        <v>378.0560752163406</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H143" t="n">
+        <v>11363.17873998612</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-388.401868371404</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.09999999999999787</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>252</v>
+      </c>
+      <c r="B144" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="C144" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D144" t="n">
+        <v>6</v>
+      </c>
+      <c r="E144" t="n">
+        <v>11663.55465720433</v>
+      </c>
+      <c r="F144" t="n">
+        <v>364.5277073184886</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H144" t="n">
+        <v>11428.82534827712</v>
+      </c>
+      <c r="I144" t="n">
+        <v>-357.8948224593099</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>252</v>
+      </c>
+      <c r="B145" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="C145" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D145" t="n">
+        <v>6</v>
+      </c>
+      <c r="E145" t="n">
+        <v>11660.89711105271</v>
+      </c>
+      <c r="F145" t="n">
+        <v>356.3486212783505</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H145" t="n">
+        <v>11424.31370015925</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-371.780247597219</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>252</v>
+      </c>
+      <c r="B146" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C146" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D146" t="n">
+        <v>6</v>
+      </c>
+      <c r="E146" t="n">
+        <v>11658.23956490108</v>
+      </c>
+      <c r="F146" t="n">
+        <v>348.1695352382121</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H146" t="n">
+        <v>11419.80205204137</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-385.6656727351283</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>252</v>
+      </c>
+      <c r="B147" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="C147" t="n">
+        <v>8</v>
+      </c>
+      <c r="D147" t="n">
+        <v>6</v>
+      </c>
+      <c r="E147" t="n">
+        <v>11674.66690832205</v>
+      </c>
+      <c r="F147" t="n">
+        <v>398.7276996444624</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H147" t="n">
+        <v>11430.6670895636</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-352.2265256221908</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>252</v>
+      </c>
+      <c r="B148" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8</v>
+      </c>
+      <c r="D148" t="n">
+        <v>6</v>
+      </c>
+      <c r="E148" t="n">
+        <v>11672.19477236706</v>
+      </c>
+      <c r="F148" t="n">
+        <v>391.1192475141012</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H148" t="n">
+        <v>11426.34085164235</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-365.5413168503229</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K148" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>252</v>
+      </c>
+      <c r="B149" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8</v>
+      </c>
+      <c r="D149" t="n">
+        <v>6</v>
+      </c>
+      <c r="E149" t="n">
+        <v>11669.72263641206</v>
+      </c>
+      <c r="F149" t="n">
+        <v>383.5107953837399</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H149" t="n">
+        <v>11422.0146137211</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-378.8561080784551</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="B150" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="C150" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D150" t="n">
+        <v>6</v>
+      </c>
+      <c r="E150" t="n">
+        <v>11692.59791544775</v>
+      </c>
+      <c r="F150" t="n">
+        <v>355.537317079767</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H150" t="n">
+        <v>11478.1313448299</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-373.1575779808607</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K150" t="n">
+        <v>3.200000000000003</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="B151" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8</v>
+      </c>
+      <c r="D151" t="n">
+        <v>6</v>
+      </c>
+      <c r="E151" t="n">
+        <v>11705.00964589056</v>
+      </c>
+      <c r="F151" t="n">
+        <v>397.7087594005479</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H151" t="n">
+        <v>11483.76688030849</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-354.0096710490411</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K151" t="n">
+        <v>3.099999999999998</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="B152" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="C152" t="n">
+        <v>8</v>
+      </c>
+      <c r="D152" t="n">
+        <v>6</v>
+      </c>
+      <c r="E152" t="n">
+        <v>11702.75091423582</v>
+      </c>
+      <c r="F152" t="n">
+        <v>390.0342476042275</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H152" t="n">
+        <v>11479.81409991268</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-367.4400666926018</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K152" t="n">
+        <v>3.500000000000004</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="B153" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8</v>
+      </c>
+      <c r="D153" t="n">
+        <v>6</v>
+      </c>
+      <c r="E153" t="n">
+        <v>11700.49218258108</v>
+      </c>
+      <c r="F153" t="n">
+        <v>382.359735807907</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H153" t="n">
+        <v>11475.86131951688</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-380.8704623361627</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>253.6</v>
+      </c>
+      <c r="B154" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="C154" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D154" t="n">
+        <v>6</v>
+      </c>
+      <c r="E154" t="n">
+        <v>11714.59796176495</v>
+      </c>
+      <c r="F154" t="n">
+        <v>430.2870619759283</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H154" t="n">
+        <v>11483.19090373652</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-355.9666715571028</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="B155" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C155" t="n">
+        <v>8</v>
+      </c>
+      <c r="D155" t="n">
+        <v>6</v>
+      </c>
+      <c r="E155" t="n">
+        <v>11735.15383817217</v>
+      </c>
+      <c r="F155" t="n">
+        <v>397.5975106948965</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H155" t="n">
+        <v>11536.5192168013</v>
+      </c>
+      <c r="I155" t="n">
+        <v>-354.204356283931</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="B156" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8</v>
+      </c>
+      <c r="D156" t="n">
+        <v>6</v>
+      </c>
+      <c r="E156" t="n">
+        <v>11733.11027210869</v>
+      </c>
+      <c r="F156" t="n">
+        <v>389.8629235860609</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H156" t="n">
+        <v>11532.9429761902</v>
+      </c>
+      <c r="I156" t="n">
+        <v>-367.7398837243934</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="B157" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C157" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D157" t="n">
+        <v>6</v>
+      </c>
+      <c r="E157" t="n">
+        <v>11745.56580726564</v>
+      </c>
+      <c r="F157" t="n">
+        <v>437.0052320144143</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H157" t="n">
+        <v>11539.26781315669</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-343.801336622547</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="B158" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D158" t="n">
+        <v>6</v>
+      </c>
+      <c r="E158" t="n">
+        <v>11743.67550865691</v>
+      </c>
+      <c r="F158" t="n">
+        <v>429.8507389387413</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H158" t="n">
+        <v>11535.84484000035</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-356.7567700298467</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K158" t="n">
+        <v>3.699999999999999</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="B159" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6</v>
+      </c>
+      <c r="E159" t="n">
+        <v>11741.78521004819</v>
+      </c>
+      <c r="F159" t="n">
+        <v>422.6962458630683</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H159" t="n">
+        <v>11532.42186684401</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-369.7122034371466</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B160" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C160" t="n">
+        <v>8</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+      <c r="E160" t="n">
+        <v>11765.07262483016</v>
+      </c>
+      <c r="F160" t="n">
+        <v>398.3820247240927</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H160" t="n">
+        <v>11588.87709345278</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-352.8314567328378</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B161" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C161" t="n">
+        <v>8</v>
+      </c>
+      <c r="D161" t="n">
+        <v>6</v>
+      </c>
+      <c r="E161" t="n">
+        <v>11763.24581786927</v>
+      </c>
+      <c r="F161" t="n">
+        <v>390.5933935011075</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H161" t="n">
+        <v>11585.68018127123</v>
+      </c>
+      <c r="I161" t="n">
+        <v>-366.461561373062</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B162" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C162" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E162" t="n">
+        <v>11745.48925420947</v>
+      </c>
+      <c r="F162" t="n">
+        <v>314.8878980136906</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H162" t="n">
+        <v>11582.72075399459</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-379.079143954298</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B163" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D163" t="n">
+        <v>6</v>
+      </c>
+      <c r="E163" t="n">
+        <v>11772.55339933498</v>
+      </c>
+      <c r="F163" t="n">
+        <v>430.2764695822175</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H163" t="n">
+        <v>11588.13723663362</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-355.9858523781468</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K163" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B164" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C164" t="n">
+        <v>8</v>
+      </c>
+      <c r="D164" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>11752.28497610396</v>
+      </c>
+      <c r="F164" t="n">
+        <v>343.8616061631958</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H164" t="n">
+        <v>11581.98089717543</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-382.2335395996071</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="B165" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D165" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11777.61586232941</v>
+      </c>
+      <c r="F165" t="n">
+        <v>316.6289569531098</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H165" t="n">
+        <v>11635.39344870287</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-376.2246170885061</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K165" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="B166" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D166" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>11775.88659220755</v>
+      </c>
+      <c r="F166" t="n">
+        <v>308.2046098065555</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H166" t="n">
+        <v>11632.55825001471</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-390.0366281078568</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="B167" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D167" t="n">
+        <v>6</v>
+      </c>
+      <c r="E167" t="n">
+        <v>11801.20632403825</v>
+      </c>
+      <c r="F167" t="n">
+        <v>431.5527252361046</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H167" t="n">
+        <v>11640.02226244765</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-353.6747948427294</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.7000000000000011</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="B168" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>8</v>
+      </c>
+      <c r="D168" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E168" t="n">
+        <v>11783.47929451002</v>
+      </c>
+      <c r="F168" t="n">
+        <v>345.1933712314267</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H168" t="n">
+        <v>11634.62130948566</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-379.9861860469675</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K168" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="B169" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>8</v>
+      </c>
+      <c r="D169" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E169" t="n">
+        <v>11781.87067114086</v>
+      </c>
+      <c r="F169" t="n">
+        <v>337.3567692346319</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H169" t="n">
+        <v>11631.90675755019</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-393.2104519165587</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>260</v>
+      </c>
+      <c r="B170" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="C170" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>11809.44543575542</v>
+      </c>
+      <c r="F170" t="n">
+        <v>319.3113641545235</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H170" t="n">
+        <v>11687.57914466877</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-371.826716909444</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>260</v>
+      </c>
+      <c r="B171" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="C171" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E171" t="n">
+        <v>11807.95206142748</v>
+      </c>
+      <c r="F171" t="n">
+        <v>310.8420174786186</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H171" t="n">
+        <v>11685.13070536366</v>
+      </c>
+      <c r="I171" t="n">
+        <v>-385.712506226916</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K171" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>260</v>
+      </c>
+      <c r="B172" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="C172" t="n">
+        <v>8</v>
+      </c>
+      <c r="D172" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>11814.40482770958</v>
+      </c>
+      <c r="F172" t="n">
+        <v>347.437473580552</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H172" t="n">
+        <v>11686.80814675992</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-376.1992633328184</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K172" t="n">
+        <v>3.400000000000002</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>260</v>
+      </c>
+      <c r="B173" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="C173" t="n">
+        <v>8</v>
+      </c>
+      <c r="D173" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E173" t="n">
+        <v>11813.01564228825</v>
+      </c>
+      <c r="F173" t="n">
+        <v>339.5590115564544</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H173" t="n">
+        <v>11684.46389636142</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-389.4941679984832</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>262</v>
+      </c>
+      <c r="B174" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C174" t="n">
+        <v>12</v>
+      </c>
+      <c r="D174" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E174" t="n">
+        <v>11828.98409354027</v>
+      </c>
+      <c r="F174" t="n">
+        <v>183.1585971303584</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H174" t="n">
+        <v>11750.60180307956</v>
+      </c>
+      <c r="I174" t="n">
+        <v>-374.560379184894</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>262</v>
+      </c>
+      <c r="B175" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="C175" t="n">
+        <v>12</v>
+      </c>
+      <c r="D175" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E175" t="n">
+        <v>11827.31401632875</v>
+      </c>
+      <c r="F175" t="n">
+        <v>171.2753803054595</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H175" t="n">
+        <v>11748.16627381276</v>
+      </c>
+      <c r="I175" t="n">
+        <v>-391.8900703878716</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>262</v>
+      </c>
+      <c r="B176" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C176" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D176" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E176" t="n">
+        <v>11831.18859545948</v>
+      </c>
+      <c r="F176" t="n">
+        <v>198.8444433392249</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H176" t="n">
+        <v>11749.74449677765</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-380.6604304883419</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K176" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>262</v>
+      </c>
+      <c r="B177" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C177" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D177" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E177" t="n">
+        <v>11829.60202210853</v>
+      </c>
+      <c r="F177" t="n">
+        <v>187.5553873555709</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H177" t="n">
+        <v>11747.39247137142</v>
+      </c>
+      <c r="I177" t="n">
+        <v>-397.3959608500745</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>262</v>
+      </c>
+      <c r="B178" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C178" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>11834.06112826329</v>
+      </c>
+      <c r="F178" t="n">
+        <v>219.283576278051</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H178" t="n">
+        <v>11749.55522136034</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-382.0071950618304</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K178" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="L178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>262</v>
+      </c>
+      <c r="B179" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="C179" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D179" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E179" t="n">
+        <v>11832.55805877293</v>
+      </c>
+      <c r="F179" t="n">
+        <v>208.588681135642</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H179" t="n">
+        <v>11747.28669981469</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-398.1485645823182</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0.5999999999999979</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B180" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C180" t="n">
+        <v>12</v>
+      </c>
+      <c r="D180" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E180" t="n">
+        <v>11863.02697610487</v>
+      </c>
+      <c r="F180" t="n">
+        <v>178.857980935459</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H180" t="n">
+        <v>11800.24767348626</v>
+      </c>
+      <c r="I180" t="n">
+        <v>-380.832111135789</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B181" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="C181" t="n">
+        <v>12</v>
+      </c>
+      <c r="D181" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E181" t="n">
+        <v>11861.68934891839</v>
+      </c>
+      <c r="F181" t="n">
+        <v>166.9327659055318</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H181" t="n">
+        <v>11798.29696717266</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-398.2230497210994</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B182" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C182" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D182" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E182" t="n">
+        <v>11866.06338981817</v>
+      </c>
+      <c r="F182" t="n">
+        <v>205.9282190533936</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H182" t="n">
+        <v>11801.44484981816</v>
+      </c>
+      <c r="I182" t="n">
+        <v>-370.159043684004</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L182" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B183" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C183" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D183" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E183" t="n">
+        <v>11864.79264399102</v>
+      </c>
+      <c r="F183" t="n">
+        <v>194.5992647749629</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H183" t="n">
+        <v>11799.56102486387</v>
+      </c>
+      <c r="I183" t="n">
+        <v>-386.9537215178181</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K183" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B184" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C184" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D184" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E184" t="n">
+        <v>11868.29722721958</v>
+      </c>
+      <c r="F184" t="n">
+        <v>225.8433281533719</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H184" t="n">
+        <v>11801.22637071104</v>
+      </c>
+      <c r="I184" t="n">
+        <v>-372.1068288055591</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K184" t="n">
         <v>2.100000000000001</v>
       </c>
-      <c r="L119" t="n">
+      <c r="L184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="B185" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C185" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D185" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E185" t="n">
+        <v>11867.09336275176</v>
+      </c>
+      <c r="F185" t="n">
+        <v>215.1106346264376</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H185" t="n">
+        <v>11799.40942711607</v>
+      </c>
+      <c r="I185" t="n">
+        <v>-388.3052458878766</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K185" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B186" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C186" t="n">
+        <v>12</v>
+      </c>
+      <c r="D186" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E186" t="n">
+        <v>11897.17666611325</v>
+      </c>
+      <c r="F186" t="n">
+        <v>175.5095745542092</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H186" t="n">
+        <v>11850.04930474849</v>
+      </c>
+      <c r="I186" t="n">
+        <v>-385.7152037751116</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K186" t="n">
+        <v>2.700000000000003</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B187" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C187" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D187" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E187" t="n">
+        <v>11899.45605056562</v>
+      </c>
+      <c r="F187" t="n">
+        <v>202.6540400401657</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H187" t="n">
+        <v>11850.94800478588</v>
+      </c>
+      <c r="I187" t="n">
+        <v>-375.0128704667718</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="L187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B188" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C188" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D188" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>11898.50212315163</v>
+      </c>
+      <c r="F188" t="n">
+        <v>191.2940214447212</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H188" t="n">
+        <v>11849.53384923356</v>
+      </c>
+      <c r="I188" t="n">
+        <v>-391.8535997880886</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K188" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B189" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C189" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E189" t="n">
+        <v>11901.132954546</v>
+      </c>
+      <c r="F189" t="n">
+        <v>222.6237569395255</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H189" t="n">
+        <v>11850.78399621295</v>
+      </c>
+      <c r="I189" t="n">
+        <v>-376.9659964709012</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K189" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="B190" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C190" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D190" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E190" t="n">
+        <v>11900.22923383801</v>
+      </c>
+      <c r="F190" t="n">
+        <v>211.8616340596309</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H190" t="n">
+        <v>11849.42004736663</v>
+      </c>
+      <c r="I190" t="n">
+        <v>-393.2088300766682</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="B191" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C191" t="n">
+        <v>12</v>
+      </c>
+      <c r="D191" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E191" t="n">
+        <v>11931.4065346644</v>
+      </c>
+      <c r="F191" t="n">
+        <v>173.1159889731816</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H191" t="n">
+        <v>11899.96786305225</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-389.20584941411</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="L191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="B192" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C192" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D192" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E192" t="n">
+        <v>11932.92711246041</v>
+      </c>
+      <c r="F192" t="n">
+        <v>200.3135153894987</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H192" t="n">
+        <v>11900.56738601587</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-378.4825956067956</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="B193" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C193" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D193" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E193" t="n">
+        <v>11934.04577542048</v>
+      </c>
+      <c r="F193" t="n">
+        <v>220.3222683037056</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H193" t="n">
+        <v>11900.45797586609</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-380.4395395045923</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1251.775</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="L193" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="B194" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C194" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D194" t="n">
+        <v>5</v>
+      </c>
+      <c r="E194" t="n">
+        <v>11963.9743848533</v>
+      </c>
+      <c r="F194" t="n">
+        <v>110.2630451703333</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H194" t="n">
+        <v>11949.67850582683</v>
+      </c>
+      <c r="I194" t="n">
+        <v>-401.5373337303284</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="B195" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>12</v>
+      </c>
+      <c r="D195" t="n">
+        <v>5</v>
+      </c>
+      <c r="E195" t="n">
+        <v>11964.68471134243</v>
+      </c>
+      <c r="F195" t="n">
+        <v>135.6931264969598</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H195" t="n">
+        <v>11949.97000773511</v>
+      </c>
+      <c r="I195" t="n">
+        <v>-391.101404129307</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="B196" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C196" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D196" t="n">
+        <v>5</v>
+      </c>
+      <c r="E196" t="n">
+        <v>11965.17724904951</v>
+      </c>
+      <c r="F196" t="n">
+        <v>153.3262489262715</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H196" t="n">
+        <v>11949.90411266772</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-393.4604840008021</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>270</v>
+      </c>
+      <c r="B197" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C197" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D197" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F197" t="n">
+        <v>109.76</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H197" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-402.2400000000002</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="L197" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>270</v>
+      </c>
+      <c r="B198" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C198" t="n">
+        <v>12</v>
+      </c>
+      <c r="D198" t="n">
+        <v>5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F198" t="n">
+        <v>135.1999999999998</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H198" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I198" t="n">
+        <v>-391.8000000000002</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K198" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>270</v>
+      </c>
+      <c r="B199" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C199" t="n">
+        <v>12</v>
+      </c>
+      <c r="D199" t="n">
+        <v>5</v>
+      </c>
+      <c r="E199" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F199" t="n">
+        <v>123.1999999999998</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H199" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I199" t="n">
+        <v>-408.8000000000002</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="L199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>270</v>
+      </c>
+      <c r="B200" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C200" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D200" t="n">
+        <v>5</v>
+      </c>
+      <c r="E200" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F200" t="n">
+        <v>152.8399999999999</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H200" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-394.16</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K200" t="n">
+        <v>2.700000000000003</v>
+      </c>
+      <c r="L200" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B201" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="C201" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D201" t="n">
+        <v>5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>12035.67380249878</v>
+      </c>
+      <c r="F201" t="n">
+        <v>122.8581326198416</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H201" t="n">
+        <v>12049.83007333163</v>
+      </c>
+      <c r="I201" t="n">
+        <v>-383.9441957056183</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B202" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C202" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D202" t="n">
+        <v>5</v>
+      </c>
+      <c r="E202" t="n">
+        <v>12036.0256151467</v>
+      </c>
+      <c r="F202" t="n">
+        <v>110.2630451703333</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H202" t="n">
+        <v>12050.32149417317</v>
+      </c>
+      <c r="I202" t="n">
+        <v>-401.5373337303284</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B203" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C203" t="n">
+        <v>12</v>
+      </c>
+      <c r="D203" t="n">
+        <v>5</v>
+      </c>
+      <c r="E203" t="n">
+        <v>12035.31528865757</v>
+      </c>
+      <c r="F203" t="n">
+        <v>135.6931264969598</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H203" t="n">
+        <v>12050.02999226489</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-391.101404129307</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K203" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="L203" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B204" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C204" t="n">
+        <v>12</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5</v>
+      </c>
+      <c r="E204" t="n">
+        <v>12035.65034832225</v>
+      </c>
+      <c r="F204" t="n">
+        <v>123.6978051164756</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H204" t="n">
+        <v>12050.50466012319</v>
+      </c>
+      <c r="I204" t="n">
+        <v>-408.094776084993</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B205" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C205" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5</v>
+      </c>
+      <c r="E205" t="n">
+        <v>12034.82275095049</v>
+      </c>
+      <c r="F205" t="n">
+        <v>153.3262489262715</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H205" t="n">
+        <v>12050.09588733228</v>
+      </c>
+      <c r="I205" t="n">
+        <v>-393.4604840008021</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K205" t="n">
+        <v>3.599999999999998</v>
+      </c>
+      <c r="L205" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="B206" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C206" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D206" t="n">
+        <v>5</v>
+      </c>
+      <c r="E206" t="n">
+        <v>12035.14105763194</v>
+      </c>
+      <c r="F206" t="n">
+        <v>141.9306936148114</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H206" t="n">
+        <v>12050.55380220735</v>
+      </c>
+      <c r="I206" t="n">
+        <v>-409.8540898874641</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0.09999999999999787</v>
+      </c>
+      <c r="L206" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="B207" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C207" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D207" t="n">
+        <v>5</v>
+      </c>
+      <c r="E207" t="n">
+        <v>12072.02313860238</v>
+      </c>
+      <c r="F207" t="n">
+        <v>111.7717884218407</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H207" t="n">
+        <v>12100.60374915888</v>
+      </c>
+      <c r="I207" t="n">
+        <v>-399.4298828393337</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K207" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="B208" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C208" t="n">
+        <v>12</v>
+      </c>
+      <c r="D208" t="n">
+        <v>5</v>
+      </c>
+      <c r="E208" t="n">
+        <v>12070.60303951535</v>
+      </c>
+      <c r="F208" t="n">
+        <v>137.1721214626302</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H208" t="n">
+        <v>12100.02097264675</v>
+      </c>
+      <c r="I208" t="n">
+        <v>-389.0061612612739</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="L208" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="B209" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C209" t="n">
+        <v>12</v>
+      </c>
+      <c r="D209" t="n">
+        <v>5</v>
+      </c>
+      <c r="E209" t="n">
+        <v>12071.27289757527</v>
+      </c>
+      <c r="F209" t="n">
+        <v>125.1908322924464</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H209" t="n">
+        <v>12100.96993823163</v>
+      </c>
+      <c r="I209" t="n">
+        <v>-405.9796542523675</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K209" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="B210" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C210" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5</v>
+      </c>
+      <c r="E210" t="n">
+        <v>12069.61834816727</v>
+      </c>
+      <c r="F210" t="n">
+        <v>154.7846165428004</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H210" t="n">
+        <v>12100.15271139853</v>
+      </c>
+      <c r="I210" t="n">
+        <v>-391.3624814647429</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K210" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="B211" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C211" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D211" t="n">
+        <v>5</v>
+      </c>
+      <c r="E211" t="n">
+        <v>12107.96450058109</v>
+      </c>
+      <c r="F211" t="n">
+        <v>114.2850532819195</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H211" t="n">
+        <v>12150.80755636723</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-395.9192906538269</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L211" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="B212" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="C212" t="n">
+        <v>12</v>
+      </c>
+      <c r="D212" t="n">
+        <v>5</v>
+      </c>
+      <c r="E212" t="n">
+        <v>12105.83573624671</v>
+      </c>
+      <c r="F212" t="n">
+        <v>139.6358316212268</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H212" t="n">
+        <v>12149.93395968284</v>
+      </c>
+      <c r="I212" t="n">
+        <v>-385.515905203262</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="L212" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="B213" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C213" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D213" t="n">
+        <v>5</v>
+      </c>
+      <c r="E213" t="n">
+        <v>12104.35965909033</v>
+      </c>
+      <c r="F213" t="n">
+        <v>157.2139656583881</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H213" t="n">
+        <v>12150.13143939311</v>
+      </c>
+      <c r="I213" t="n">
+        <v>-387.8676283510906</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="B214" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C214" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E214" t="n">
+        <v>12150.67032628464</v>
+      </c>
+      <c r="F214" t="n">
+        <v>56.74377902900505</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H214" t="n">
+        <v>12202.03521024532</v>
+      </c>
+      <c r="I214" t="n">
+        <v>-401.1844781201978</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L214" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="B215" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C215" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E215" t="n">
+        <v>12149.43970927309</v>
+      </c>
+      <c r="F215" t="n">
+        <v>67.71497685653799</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H215" t="n">
+        <v>12202.81103401348</v>
+      </c>
+      <c r="I215" t="n">
+        <v>-408.1011028375558</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="B216" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C216" t="n">
+        <v>12</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E216" t="n">
+        <v>12147.67404138694</v>
+      </c>
+      <c r="F216" t="n">
+        <v>83.45626069604168</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H216" t="n">
+        <v>12203.05180690704</v>
+      </c>
+      <c r="I216" t="n">
+        <v>-410.2476415429427</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>278</v>
+      </c>
+      <c r="B217" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="C217" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E217" t="n">
+        <v>12188.1174971057</v>
+      </c>
+      <c r="F217" t="n">
+        <v>61.47445684339414</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H217" t="n">
+        <v>12252.2484620281</v>
+      </c>
+      <c r="I217" t="n">
+        <v>-394.8410692327216</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L217" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>278</v>
+      </c>
+      <c r="B218" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="C218" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E218" t="n">
+        <v>12189.95458203837</v>
+      </c>
+      <c r="F218" t="n">
+        <v>48.40291833600531</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H218" t="n">
+        <v>12254.71182591509</v>
+      </c>
+      <c r="I218" t="n">
+        <v>-412.3688140494475</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L218" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>278</v>
+      </c>
+      <c r="B219" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C219" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E219" t="n">
+        <v>12186.5810260711</v>
+      </c>
+      <c r="F219" t="n">
+        <v>72.40701632230116</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H219" t="n">
+        <v>12253.21710681078</v>
+      </c>
+      <c r="I219" t="n">
+        <v>-401.7333349911629</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K219" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>278</v>
+      </c>
+      <c r="B220" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="C220" t="n">
+        <v>12</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E220" t="n">
+        <v>12184.37652415189</v>
+      </c>
+      <c r="F220" t="n">
+        <v>88.09286253116761</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H220" t="n">
+        <v>12253.51772070885</v>
+      </c>
+      <c r="I220" t="n">
+        <v>-403.8723140196445</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1300.775</v>
+      </c>
+      <c r="K220" t="n">
+        <v>2.700000000000003</v>
+      </c>
+      <c r="L220" t="n">
         <v>2</v>
       </c>
     </row>
